--- a/saida/valuation_vale_csn_gerdau.xlsx
+++ b/saida/valuation_vale_csn_gerdau.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="772">
   <si>
     <t xml:space="preserve">Valuation de Vale, CSN e Gerdau</t>
   </si>
@@ -847,7 +847,7 @@
     <t xml:space="preserve">(-) Juros da dívida</t>
   </si>
   <si>
-    <t xml:space="preserve">Dívida do início do ano × custo da dívida.</t>
+    <t xml:space="preserve">Dívida do início do ano × juros pagos sobre a dívida (aba Premissas).</t>
   </si>
   <si>
     <t xml:space="preserve">(+/-) Resultado financeiro</t>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">Custo da dívida antes do imposto (Kd)</t>
   </si>
   <si>
-    <t xml:space="preserve">O juro que a empresa paga para tomar dinheiro emprestado.</t>
+    <t xml:space="preserve">O que a dívida custa à empresa, em reais. Vem do custo que ela divulga (aba Premissas).</t>
   </si>
   <si>
     <t xml:space="preserve">Alíquota de IR e CSLL</t>
@@ -2203,6 +2203,12 @@
     <t xml:space="preserve">Iguais nos três cenários, gerais</t>
   </si>
   <si>
+    <t xml:space="preserve">Juros pagos sobre a dívida (% do saldo inicial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo da dívida no WACC, em reais, antes do imposto (Kd)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dividendos (% do lucro)</t>
   </si>
   <si>
@@ -2233,13 +2239,13 @@
     <t xml:space="preserve">De onde veio</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.8% ao ano).</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,8% ao ano).</t>
   </si>
   <si>
     <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Daí até 2030 em linha reta. Faixa: margem EBITDA de 2021 a 2025, sem perdas por recuperabilidade. Pessimista é o segundo pior ano, moderado a mediana e otimista o segundo melhor.</t>
   </si>
   <si>
-    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12.2% a 15.3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
+    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12,2% a 15,3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
   </si>
   <si>
     <t xml:space="preserve">Vendas, administrativas e outras, sem perdas por recuperabilidade. Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
@@ -2260,7 +2266,10 @@
     <t xml:space="preserve">Alíquota nominal: IRPJ 25% + CSLL 9%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 17.8%.</t>
+    <t xml:space="preserve">Custo médio de 5,6% ao ano em dólar, depois de swaps (formulário 6-K do 2T26, SEC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo médio de 5,6% ao ano em dólar, depois de swaps (formulário 6-K do 2T26, SEC). A parte em dólar foi trazida para reais pela diferença de inflação (3,5% no Brasil, 2,0% nos EUA).</t>
   </si>
   <si>
     <t xml:space="preserve">Mediana 2023-2025 da receita financeira sobre o caixa médio.</t>
@@ -2272,7 +2281,7 @@
     <t xml:space="preserve">Tesouro prefixado de dez anos (em reais, nominal).</t>
   </si>
   <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.64.</t>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,64.</t>
   </si>
   <si>
     <t xml:space="preserve">Damodaran, mercado maduro. O risco-país já está no juro em reais.</t>
@@ -2311,22 +2320,28 @@
     <t xml:space="preserve">Pregão do preço acima.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10.0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 14.2%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1.48.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.1% ao ano).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 19.3%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.71.</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10,0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A CSN não divulga custo médio. Juros pagos em 2025 (R$ 4.268 mi, linha "Juros pagos" do fluxo de caixa na CVM) sobre a dívida bruta média do ano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A empresa não divulga custo médio: mantido o piso, a taxa do Tesouro prefixado de dez anos, sem spread de crédito.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1,48.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,1% ao ano).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53% da dívida em dólar a 6,13% ao ano e 46% em reais a CDI - 0,15% (formulário 6-K do 2T26, SEC). CDI de 13,65%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53% da dívida em dólar a 6,13% ao ano e 46% em reais a CDI - 0,15% (formulário 6-K do 2T26, SEC). CDI de 13,65%. A parte em dólar foi trazida para reais pela diferença de inflação (3,5% no Brasil, 2,0% nos EUA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,71.</t>
   </si>
   <si>
     <t xml:space="preserve">Dados da CVM</t>
@@ -2986,11 +3001,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="382606"/>
-        <c:axId val="86157532"/>
+        <c:axId val="77798981"/>
+        <c:axId val="56045745"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="382606"/>
+        <c:axId val="77798981"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3022,7 +3037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86157532"/>
+        <c:crossAx val="56045745"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3030,7 +3045,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86157532"/>
+        <c:axId val="56045745"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3072,7 +3087,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="382606"/>
+        <c:crossAx val="77798981"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4124,11 +4139,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58037023"/>
-        <c:axId val="28988576"/>
+        <c:axId val="62519026"/>
+        <c:axId val="86150834"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58037023"/>
+        <c:axId val="62519026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4160,7 +4175,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28988576"/>
+        <c:crossAx val="86150834"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4168,7 +4183,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28988576"/>
+        <c:axId val="86150834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,7 +4225,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58037023"/>
+        <c:crossAx val="62519026"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4790,11 +4805,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="94622550"/>
-        <c:axId val="19950160"/>
+        <c:axId val="98891909"/>
+        <c:axId val="50635579"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="94622550"/>
+        <c:axId val="98891909"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4836,12 +4851,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19950160"/>
+        <c:crossAx val="50635579"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="19950160"/>
+        <c:axId val="50635579"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4883,7 +4898,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94622550"/>
+        <c:crossAx val="98891909"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5355,24 +5370,24 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF(ISNUMBER(G12),MIN(MAX(G12,MIN(D12:F12)),MAX(D12:F12)),CHOOSE(Painel!$Y$9,D12,E12,F12))</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$D$9</f>
-        <v>0.15675595075</v>
+        <v>0.14677675075</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$E$9</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$F$9</f>
-        <v>0.12555595075</v>
+        <v>0.11557675075</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="11" t="n">
         <f aca="false">WACC!$D$19</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5397,7 +5412,7 @@
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>25</v>
@@ -5421,7 +5436,7 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">'Valor justo'!D31</f>
-        <v>0.242894562985227</v>
+        <v>0.403675433288633</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>29</v>
@@ -5433,7 +5448,7 @@
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>388137.318310682</v>
+        <v>432425.186610631</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>31</v>
@@ -5445,7 +5460,7 @@
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>342361.318310682</v>
+        <v>386649.186610631</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>33</v>
@@ -5457,7 +5472,7 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">'Valor justo'!D32</f>
-        <v>0.734038701125195</v>
+        <v>0.756569234886324</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>35</v>
@@ -5469,7 +5484,7 @@
       </c>
       <c r="C22" s="16" t="n">
         <f aca="false">'Valor justo'!D43</f>
-        <v>71.9711006308269</v>
+        <v>81.7012498309882</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>37</v>
@@ -5504,7 +5519,7 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">WACC!D22</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>43</v>
@@ -5516,7 +5531,7 @@
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>103229.505319693</v>
+        <v>105265.59403105</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>45</v>
@@ -5528,7 +5543,7 @@
       </c>
       <c r="C28" s="17" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>284907.812990989</v>
+        <v>327159.592579581</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>45</v>
@@ -5540,7 +5555,7 @@
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>388137.318310682</v>
+        <v>432425.186610631</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>45</v>
@@ -5552,7 +5567,7 @@
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>342361.318310682</v>
+        <v>386649.186610631</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>45</v>
@@ -5564,7 +5579,7 @@
       </c>
       <c r="C31" s="16" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>50</v>
@@ -10509,7 +10524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L154"/>
+  <dimension ref="B1:L158"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -10571,19 +10586,19 @@
         <v>714</v>
       </c>
       <c r="C7" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(C$1:C$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0209</v>
       </c>
       <c r="D7" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0378</v>
       </c>
       <c r="F7" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0683</v>
       </c>
       <c r="L7" s="7" t="s">
@@ -10595,19 +10610,19 @@
         <v>18</v>
       </c>
       <c r="C8" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(C$1:C$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.3459</v>
       </c>
       <c r="D8" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.3484</v>
       </c>
       <c r="E8" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.3936</v>
       </c>
       <c r="F8" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.4542</v>
       </c>
     </row>
@@ -10616,15 +10631,15 @@
         <v>715</v>
       </c>
       <c r="D9" s="32" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0156</v>
       </c>
       <c r="E9" s="32" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="F9" s="32" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>-0.0156</v>
       </c>
     </row>
@@ -10655,23 +10670,23 @@
         <v>717</v>
       </c>
       <c r="D12" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.083</v>
       </c>
       <c r="E12" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0815</v>
       </c>
       <c r="F12" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.08</v>
       </c>
       <c r="G12" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0785</v>
       </c>
       <c r="H12" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.077</v>
       </c>
     </row>
@@ -10680,23 +10695,23 @@
         <v>718</v>
       </c>
       <c r="D13" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="E13" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="F13" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="G13" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="H13" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
     </row>
@@ -10705,23 +10720,23 @@
         <v>719</v>
       </c>
       <c r="D14" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.146</v>
       </c>
       <c r="E14" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.1449</v>
       </c>
       <c r="F14" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.1438</v>
       </c>
       <c r="G14" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.1427</v>
       </c>
       <c r="H14" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.1415</v>
       </c>
     </row>
@@ -10730,23 +10745,23 @@
         <v>720</v>
       </c>
       <c r="D15" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="E15" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="F15" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="G15" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="H15" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
     </row>
@@ -10755,23 +10770,23 @@
         <v>219</v>
       </c>
       <c r="D16" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="E16" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="F16" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="G16" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="H16" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
     </row>
@@ -10780,23 +10795,23 @@
         <v>221</v>
       </c>
       <c r="D17" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="E17" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="F17" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="G17" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="H17" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
     </row>
@@ -10805,23 +10820,23 @@
         <v>223</v>
       </c>
       <c r="D18" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="E18" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="F18" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="G18" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="H18" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
     </row>
@@ -10830,23 +10845,23 @@
         <v>721</v>
       </c>
       <c r="D19" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="E19" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="F19" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="G19" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="H19" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
     </row>
@@ -10869,386 +10884,372 @@
         <v>360</v>
       </c>
       <c r="D22" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0.34</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>358</v>
+        <v>723</v>
       </c>
       <c r="D23" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.1291</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.056</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>491</v>
+        <v>724</v>
       </c>
       <c r="D24" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.0936</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0715</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>723</v>
+        <v>491</v>
       </c>
       <c r="D25" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.679</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>347</v>
+        <v>725</v>
       </c>
       <c r="D26" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.1291</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.679</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D27" s="50" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.7558</v>
+        <v>347</v>
+      </c>
+      <c r="D27" s="48" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="D28" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.0423</v>
+        <v>349</v>
+      </c>
+      <c r="D28" s="50" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.7558</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>724</v>
+        <v>351</v>
       </c>
       <c r="D29" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D30" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.2625</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>401</v>
+        <v>727</v>
       </c>
       <c r="D31" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>0.035</v>
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.2625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D32" s="51" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>1</v>
+        <v>401</v>
+      </c>
+      <c r="D32" s="48" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>0.035</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="D33" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>728</v>
+      </c>
+      <c r="D33" s="51" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D36" s="52" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>46203</v>
-      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D37" s="53" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>4072.366</v>
+        <v>731</v>
+      </c>
+      <c r="D37" s="52" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>46203</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D38" s="41" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>67.64</v>
+        <v>422</v>
+      </c>
+      <c r="D38" s="53" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>4072.366</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D39" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
-        <v>275454.8362</v>
+        <v>732</v>
+      </c>
+      <c r="D39" s="41" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>67.64</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D40" s="54" t="str">
-        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>378</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <v>275454.8362</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="D41" s="54" t="str">
+        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
         <v>2026-10-08</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="47" t="s">
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="47" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="C45" s="12" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>0.0683</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>733</v>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>18</v>
+        <v>714</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0.3459</v>
+        <v>0.0209</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.3484</v>
+        <v>0</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.3936</v>
+        <v>0.0378</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.4542</v>
+        <v>0.0683</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="s">
         <v>715</v>
       </c>
-      <c r="D47" s="55" t="n">
+      <c r="D48" s="55" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E47" s="55" t="n">
+      <c r="E48" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="55" t="n">
+      <c r="F48" s="55" t="n">
         <v>-0.0156</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8" t="s">
+      <c r="I48" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9" t="s">
+      <c r="C50" s="9"/>
+      <c r="D50" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E50" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F50" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G50" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H50" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="I49" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>0.0785</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>736</v>
+      <c r="I50" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D51" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="E51" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="F51" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="G51" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="H51" s="56" t="n">
-        <v>-1570</v>
+        <v>717</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0.077</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>719</v>
-      </c>
-      <c r="D52" s="12" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>0.1449</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>0.1438</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>0.1427</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>0.1415</v>
+        <v>718</v>
+      </c>
+      <c r="D52" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="E52" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="F52" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="G52" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="H52" s="56" t="n">
+        <v>-1570</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.0569</v>
+        <v>0.146</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0569</v>
+        <v>0.1449</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.0569</v>
+        <v>0.1438</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.0569</v>
+        <v>0.1427</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0.0569</v>
+        <v>0.1415</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D54" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="E54" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="F54" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="G54" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="H54" s="57" t="n">
-        <v>21.598</v>
+        <v>720</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>0.0569</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>739</v>
@@ -11256,464 +11257,452 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D55" s="57" t="n">
-        <v>98.067</v>
+        <v>21.598</v>
       </c>
       <c r="E55" s="57" t="n">
-        <v>98.067</v>
+        <v>21.598</v>
       </c>
       <c r="F55" s="57" t="n">
-        <v>98.067</v>
+        <v>21.598</v>
       </c>
       <c r="G55" s="57" t="n">
-        <v>98.067</v>
+        <v>21.598</v>
       </c>
       <c r="H55" s="57" t="n">
-        <v>98.067</v>
+        <v>21.598</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D56" s="57" t="n">
-        <v>91.9277</v>
+        <v>98.067</v>
       </c>
       <c r="E56" s="57" t="n">
-        <v>91.9277</v>
+        <v>98.067</v>
       </c>
       <c r="F56" s="57" t="n">
-        <v>91.9277</v>
+        <v>98.067</v>
       </c>
       <c r="G56" s="57" t="n">
-        <v>91.9277</v>
+        <v>98.067</v>
       </c>
       <c r="H56" s="57" t="n">
-        <v>91.9277</v>
+        <v>98.067</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D57" s="57" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="E57" s="57" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="F57" s="57" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="G57" s="57" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="H57" s="57" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="D57" s="56" t="n">
+      <c r="D58" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="56" t="n">
+      <c r="E58" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="56" t="n">
+      <c r="F58" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="56" t="n">
+      <c r="G58" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="56" t="n">
+      <c r="H58" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="8" t="s">
+      <c r="I58" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9" t="s">
+      <c r="C60" s="9"/>
+      <c r="D60" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>741</v>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.1291</v>
+        <v>0.34</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>491</v>
+        <v>723</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.0936</v>
+        <v>0.056</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.679</v>
+        <v>0.0715</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>347</v>
+        <v>491</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.1291</v>
+        <v>0.0936</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D65" s="58" t="n">
-        <v>0.7558</v>
+        <v>725</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>0.679</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.0423</v>
+        <v>0.1291</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>0</v>
+        <v>349</v>
+      </c>
+      <c r="D67" s="58" t="n">
+        <v>0.7558</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>725</v>
+        <v>351</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.2625</v>
+        <v>0.0423</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>401</v>
+        <v>726</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D70" s="59" t="n">
-        <v>1</v>
+        <v>727</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>0.2625</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="D71" s="56" t="n">
+        <v>401</v>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="D72" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="D73" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9" t="s">
+      <c r="I73" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D74" s="60" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D75" s="61" t="n">
-        <v>4072.366</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>754</v>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D76" s="62" t="n">
-        <v>67.64</v>
+        <v>731</v>
+      </c>
+      <c r="D76" s="60" t="n">
+        <v>46203</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D77" s="56" t="n">
-        <v>275454.8362</v>
+        <v>422</v>
+      </c>
+      <c r="D77" s="61" t="n">
+        <v>4072.366</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D78" s="63" t="s">
-        <v>757</v>
+        <v>732</v>
+      </c>
+      <c r="D78" s="62" t="n">
+        <v>67.64</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="47" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="D79" s="56" t="n">
+        <v>275454.8362</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="D80" s="63" t="s">
+        <v>760</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="47" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="8" t="s">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D84" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E82" s="9" t="s">
+      <c r="E84" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F84" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="C83" s="12" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="D83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>0.0778</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>0.1713</v>
-      </c>
-      <c r="D84" s="12" t="n">
-        <v>0.1884</v>
-      </c>
-      <c r="E84" s="12" t="n">
-        <v>0.2002</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="I84" s="2" t="s">
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="8" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0.0778</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="0" t="s">
         <v>715</v>
       </c>
-      <c r="D85" s="55" t="n">
+      <c r="D87" s="55" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E85" s="55" t="n">
+      <c r="E87" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="55" t="n">
+      <c r="F87" s="55" t="n">
         <v>-0.0156</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="8" t="s">
+      <c r="I87" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9" t="s">
+      <c r="C89" s="9"/>
+      <c r="D89" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E89" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F87" s="9" t="s">
+      <c r="F89" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="G89" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="H89" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="I87" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="D88" s="12" t="n">
-        <v>0.2146</v>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>0.2001</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>0.1713</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>0.1569</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D89" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="E89" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="F89" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="G89" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="H89" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>737</v>
+      <c r="I89" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="0" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.1326</v>
+        <v>0.2146</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.1237</v>
+        <v>0.2001</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.1148</v>
+        <v>0.1857</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.1059</v>
+        <v>0.1713</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0.097</v>
+        <v>0.1569</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>738</v>
@@ -11721,68 +11710,68 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="D91" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>0.0983</v>
+        <v>718</v>
+      </c>
+      <c r="D91" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="E91" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="F91" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="G91" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="H91" s="56" t="n">
+        <v>351.131</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D92" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="E92" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="F92" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="G92" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="H92" s="57" t="n">
-        <v>19.5303</v>
+        <v>719</v>
+      </c>
+      <c r="D92" s="12" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>0.097</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="D93" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="E93" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="F93" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="G93" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="H93" s="57" t="n">
-        <v>135.0709</v>
+        <v>720</v>
+      </c>
+      <c r="D93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>0.0983</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>739</v>
@@ -11790,94 +11779,118 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="0" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D94" s="57" t="n">
-        <v>92.5353</v>
+        <v>19.5303</v>
       </c>
       <c r="E94" s="57" t="n">
-        <v>92.5353</v>
+        <v>19.5303</v>
       </c>
       <c r="F94" s="57" t="n">
-        <v>92.5353</v>
+        <v>19.5303</v>
       </c>
       <c r="G94" s="57" t="n">
-        <v>92.5353</v>
+        <v>19.5303</v>
       </c>
       <c r="H94" s="57" t="n">
-        <v>92.5353</v>
+        <v>19.5303</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D95" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="E95" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="F95" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="G95" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="H95" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D96" s="57" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="E96" s="57" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="F96" s="57" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="G96" s="57" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="H96" s="57" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="D95" s="56" t="n">
+      <c r="D97" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="56" t="n">
+      <c r="E97" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F95" s="56" t="n">
+      <c r="F97" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="56" t="n">
+      <c r="G97" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="56" t="n">
+      <c r="H97" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="I95" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="8" t="s">
+      <c r="I97" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9" t="s">
+      <c r="C99" s="9"/>
+      <c r="D99" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="D98" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>760</v>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="0" t="s">
-        <v>491</v>
+        <v>360</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.0772</v>
+        <v>0.34</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>743</v>
@@ -11888,40 +11901,40 @@
         <v>723</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.242</v>
+        <v>0.0777</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="0" t="s">
-        <v>347</v>
+        <v>724</v>
       </c>
       <c r="D102" s="12" t="n">
         <v>0.1291</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>745</v>
+        <v>764</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D103" s="58" t="n">
-        <v>1.483</v>
+        <v>491</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>0.0772</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="0" t="s">
-        <v>351</v>
+        <v>725</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.0423</v>
+        <v>0.242</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>747</v>
@@ -11929,10 +11942,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="0" t="s">
-        <v>724</v>
+        <v>347</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0</v>
+        <v>0.1291</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>748</v>
@@ -11940,21 +11953,21 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>0.8635</v>
+        <v>349</v>
+      </c>
+      <c r="D106" s="58" t="n">
+        <v>1.483</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.035</v>
+        <v>0.0423</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>750</v>
@@ -11964,8 +11977,8 @@
       <c r="B108" s="0" t="s">
         <v>726</v>
       </c>
-      <c r="D108" s="59" t="n">
-        <v>1</v>
+      <c r="D108" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>751</v>
@@ -11975,68 +11988,68 @@
       <c r="B109" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="D109" s="56" t="n">
-        <v>0</v>
+      <c r="D109" s="12" t="n">
+        <v>0.8635</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>752</v>
       </c>
     </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="8" t="s">
-        <v>732</v>
+      <c r="D111" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="D112" s="60" t="n">
-        <v>46203</v>
+      <c r="D112" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D113" s="61" t="n">
-        <v>1326.0939</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="D114" s="62" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>755</v>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D115" s="56" t="n">
-        <v>8433.9575</v>
+        <v>731</v>
+      </c>
+      <c r="D115" s="60" t="n">
+        <v>46203</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>756</v>
@@ -12044,233 +12057,197 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D116" s="63" t="s">
+        <v>422</v>
+      </c>
+      <c r="D116" s="61" t="n">
+        <v>1326.0939</v>
+      </c>
+      <c r="I116" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="I116" s="2" t="s">
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="D117" s="62" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I117" s="2" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="47" t="s">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="D118" s="56" t="n">
+        <v>8433.9575</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="D119" s="63" t="s">
+        <v>760</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="8" t="s">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="C123" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="D120" s="9" t="s">
+      <c r="D123" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="E123" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F120" s="9" t="s">
+      <c r="F123" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="0" t="s">
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="0" t="s">
         <v>714</v>
       </c>
-      <c r="C121" s="12" t="n">
+      <c r="C124" s="12" t="n">
         <v>-0.0045</v>
       </c>
-      <c r="D121" s="12" t="n">
+      <c r="D124" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="12" t="n">
+      <c r="E124" s="12" t="n">
         <v>0.0378</v>
       </c>
-      <c r="F121" s="12" t="n">
+      <c r="F124" s="12" t="n">
         <v>0.061</v>
       </c>
-      <c r="I121" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="0" t="s">
+      <c r="I124" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C122" s="12" t="n">
+      <c r="C125" s="12" t="n">
         <v>0.1538</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D125" s="12" t="n">
         <v>0.1613</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>0.1971</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F125" s="12" t="n">
         <v>0.2506</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="D123" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E123" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E125" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G125" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>732</v>
+      <c r="I125" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="D126" s="12" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="E126" s="12" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>0.0279</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>0.0261</v>
+        <v>715</v>
+      </c>
+      <c r="D126" s="55" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E126" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="55" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D127" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="E127" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="F127" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="G127" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="H127" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="I127" s="2" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="0" t="s">
-        <v>719</v>
-      </c>
-      <c r="D128" s="12" t="n">
-        <v>0.0779</v>
-      </c>
-      <c r="E128" s="12" t="n">
-        <v>0.0773</v>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>0.0767</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>0.0762</v>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>738</v>
+      <c r="B128" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="0" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>0.0887</v>
+        <v>0.0332</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>0.0887</v>
+        <v>0.0315</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>0.0887</v>
+        <v>0.0297</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.0887</v>
+        <v>0.0279</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0.0887</v>
+        <v>0.0261</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="E130" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="F130" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="G130" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="H130" s="57" t="n">
-        <v>25.1348</v>
+        <v>718</v>
+      </c>
+      <c r="D130" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="E130" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="F130" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="G130" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="H130" s="56" t="n">
+        <v>563.158</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>739</v>
@@ -12278,45 +12255,45 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="D131" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="E131" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="F131" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="G131" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="H131" s="57" t="n">
-        <v>92.3738</v>
+        <v>719</v>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>0.0773</v>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>0.0756</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="D132" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="E132" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="F132" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="G132" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="H132" s="57" t="n">
-        <v>31.414</v>
+        <v>720</v>
+      </c>
+      <c r="D132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>0.0887</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>739</v>
@@ -12324,244 +12301,324 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="D133" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="56" t="n">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="D133" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="E133" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="F133" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="G133" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="H133" s="57" t="n">
+        <v>25.1348</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D134" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="E134" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="F134" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="G134" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="H134" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="8" t="s">
-        <v>732</v>
+      <c r="B135" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="D135" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="E135" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="F135" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="G135" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="H135" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="D136" s="12" t="n">
-        <v>0.34</v>
+        <v>721</v>
+      </c>
+      <c r="D136" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="D137" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="D138" s="12" t="n">
-        <v>0.1235</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>743</v>
+      <c r="B138" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="9"/>
+      <c r="I138" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="0" t="s">
-        <v>723</v>
+        <v>360</v>
       </c>
       <c r="D139" s="12" t="n">
-        <v>0.3602</v>
+        <v>0.34</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="0" t="s">
-        <v>347</v>
+        <v>723</v>
       </c>
       <c r="D140" s="12" t="n">
-        <v>0.1291</v>
+        <v>0.0955</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D141" s="58" t="n">
-        <v>0.7921</v>
+        <v>724</v>
+      </c>
+      <c r="D141" s="12" t="n">
+        <v>0.1039</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="0" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>0.0423</v>
+        <v>0.1235</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D143" s="12" t="n">
-        <v>0</v>
+        <v>0.3602</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="0" t="s">
-        <v>725</v>
+        <v>347</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>0.2273</v>
+        <v>0.1291</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="D145" s="12" t="n">
-        <v>0.035</v>
+        <v>349</v>
+      </c>
+      <c r="D145" s="58" t="n">
+        <v>0.7921</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>750</v>
+        <v>769</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D146" s="59" t="n">
-        <v>1</v>
+        <v>351</v>
+      </c>
+      <c r="D146" s="12" t="n">
+        <v>0.0423</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="D147" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="2" t="s">
+      <c r="D148" s="12" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="I148" s="2" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E149" s="9"/>
-      <c r="F149" s="9"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
-      <c r="I149" s="8" t="s">
-        <v>732</v>
+      <c r="B149" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D150" s="60" t="n">
-        <v>46203</v>
+        <v>728</v>
+      </c>
+      <c r="D150" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D151" s="61" t="n">
-        <v>1963.1806</v>
+        <v>729</v>
+      </c>
+      <c r="D151" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="0" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="D152" s="62" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D153" s="56" t="n">
-        <v>46089.0479</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>756</v>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
+      <c r="I153" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="D154" s="63" t="s">
+      <c r="D154" s="60" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="D155" s="61" t="n">
+        <v>1963.1806</v>
+      </c>
+      <c r="I155" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="I154" s="2" t="s">
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="D156" s="62" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="I156" s="2" t="s">
         <v>758</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="D157" s="56" t="n">
+        <v>46089.0479</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="D158" s="63" t="s">
+        <v>760</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -12590,12 +12647,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16031,7 +16088,7 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">WACC!D14</f>
-        <v>0.085206</v>
+        <v>0.04719</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16049,7 +16106,7 @@
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">WACC!D19</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16058,7 +16115,7 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">WACC!D22</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>72</v>
@@ -16093,7 +16150,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">'Valor justo'!E10</f>
-        <v>0.875829030426722</v>
+        <v>0.883587455256839</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>77</v>
@@ -16105,7 +16162,7 @@
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">'Valor justo'!E11</f>
-        <v>23696.9148208663</v>
+        <v>23906.8310556065</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16114,7 +16171,7 @@
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>103229.505319693</v>
+        <v>105265.59403105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16158,7 +16215,7 @@
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">'Valor justo'!D17</f>
-        <v>516407.475225762</v>
+        <v>569989.379756602</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16167,7 +16224,7 @@
       </c>
       <c r="C34" s="21" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>284907.812990989</v>
+        <v>327159.592579581</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16190,7 +16247,7 @@
       </c>
       <c r="C38" s="17" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>103229.505319693</v>
+        <v>105265.59403105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16199,7 +16256,7 @@
       </c>
       <c r="C39" s="17" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>284907.812990989</v>
+        <v>327159.592579581</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16208,7 +16265,7 @@
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>388137.318310682</v>
+        <v>432425.186610631</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16231,7 +16288,7 @@
       </c>
       <c r="C44" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>388137.318310682</v>
+        <v>432425.186610631</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16276,7 +16333,7 @@
       </c>
       <c r="C48" s="21" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>342361.318310682</v>
+        <v>386649.186610631</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16299,7 +16356,7 @@
       </c>
       <c r="C52" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>342361.318310682</v>
+        <v>386649.186610631</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16317,7 +16374,7 @@
       </c>
       <c r="C54" s="25" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16335,7 +16392,7 @@
       </c>
       <c r="C56" s="11" t="n">
         <f aca="false">'Valor justo'!D31</f>
-        <v>0.242894562985227</v>
+        <v>0.403675433288633</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>106</v>
@@ -19543,24 +19600,24 @@
         <v>268</v>
       </c>
       <c r="D17" s="17" t="n">
-        <f aca="false">C38*Premissas!$D$24</f>
+        <f aca="false">C38*Premissas!$D$25</f>
         <v>3896.4744</v>
       </c>
       <c r="E17" s="17" t="n">
-        <f aca="false">D38*Premissas!$D$24</f>
-        <v>3543.0526541656</v>
+        <f aca="false">D38*Premissas!$D$25</f>
+        <v>3693.02185404644</v>
       </c>
       <c r="F17" s="17" t="n">
-        <f aca="false">E38*Premissas!$D$24</f>
-        <v>3245.42202532735</v>
+        <f aca="false">E38*Premissas!$D$25</f>
+        <v>3548.33432871972</v>
       </c>
       <c r="G17" s="17" t="n">
-        <f aca="false">F38*Premissas!$D$24</f>
-        <v>3029.4355659922</v>
+        <f aca="false">F38*Premissas!$D$25</f>
+        <v>3488.32384932126</v>
       </c>
       <c r="H17" s="17" t="n">
-        <f aca="false">G38*Premissas!$D$24</f>
-        <v>2901.01518499671</v>
+        <f aca="false">G38*Premissas!$D$25</f>
+        <v>3518.97246691831</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>269</v>
@@ -19572,23 +19629,23 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">C42*Premissas!$D$23</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">D42*Premissas!$D$23</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">E42*Premissas!$D$23</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">F42*Premissas!$D$23</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="H18" s="17" t="n">
         <f aca="false">G42*Premissas!$D$23</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>271</v>
@@ -19604,23 +19661,23 @@
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">D17-D18</f>
-        <v>-9459.8243</v>
+        <v>-1897.1176</v>
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">E17-E18</f>
-        <v>-9813.2460458344</v>
+        <v>-2100.57014595356</v>
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">F17-F18</f>
-        <v>-10110.8766746726</v>
+        <v>-2245.25767128028</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">G17-G18</f>
-        <v>-10326.8631340078</v>
+        <v>-2305.26815067874</v>
       </c>
       <c r="H19" s="17" t="n">
         <f aca="false">H17-H18</f>
-        <v>-10455.2835150033</v>
+        <v>-2274.61953308169</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>273</v>
@@ -19636,23 +19693,23 @@
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">D16+D19</f>
-        <v>49505.60376945</v>
+        <v>57068.31046945</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">E16+E19</f>
-        <v>53827.0975468693</v>
+        <v>61539.7734467501</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">F16+F19</f>
-        <v>58511.6418286614</v>
+        <v>66377.2608320537</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">G16+G19</f>
-        <v>63599.4715671608</v>
+        <v>71621.0665504898</v>
       </c>
       <c r="H20" s="17" t="n">
         <f aca="false">H16+H19</f>
-        <v>69111.6621320382</v>
+        <v>77292.3261139598</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>274</v>
@@ -19668,23 +19725,23 @@
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">MAX(0,D20-D13)*Premissas!$D$22</f>
-        <v>17365.705281613</v>
+        <v>19937.025559613</v>
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">MAX(0,E20-E13)*Premissas!$D$22</f>
-        <v>18835.0131659356</v>
+        <v>21457.322971895</v>
       </c>
       <c r="F21" s="17" t="n">
         <f aca="false">MAX(0,F20-F13)*Premissas!$D$22</f>
-        <v>20427.7582217449</v>
+        <v>23102.0686828983</v>
       </c>
       <c r="G21" s="17" t="n">
         <f aca="false">MAX(0,G20-G13)*Premissas!$D$22</f>
-        <v>22157.6203328347</v>
+        <v>24884.9626271665</v>
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">MAX(0,H20-H13)*Premissas!$D$22</f>
-        <v>24031.765124893</v>
+        <v>26813.1908787463</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>276</v>
@@ -19700,23 +19757,23 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D20-D21</f>
-        <v>32139.898487837</v>
+        <v>37131.284909837</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">E20-E21</f>
-        <v>34992.0843809337</v>
+        <v>40082.4504748551</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">F20-F21</f>
-        <v>38083.8836069165</v>
+        <v>43275.1921491555</v>
       </c>
       <c r="G22" s="31" t="n">
         <f aca="false">G20-G21</f>
-        <v>41441.8512343261</v>
+        <v>46736.1039233233</v>
       </c>
       <c r="H22" s="31" t="n">
         <f aca="false">H20-H21</f>
-        <v>45079.8970071452</v>
+        <v>50479.1352352134</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>278</v>
@@ -19969,24 +20026,24 @@
         <v>291</v>
       </c>
       <c r="D34" s="17" t="n">
-        <f aca="false">MAX(0,D22)*Premissas!$D$25</f>
-        <v>21822.9910732413</v>
+        <f aca="false">MAX(0,D22)*Premissas!$D$26</f>
+        <v>25212.1424537793</v>
       </c>
       <c r="E34" s="17" t="n">
-        <f aca="false">MAX(0,E22)*Premissas!$D$25</f>
-        <v>23759.625294654</v>
+        <f aca="false">MAX(0,E22)*Premissas!$D$26</f>
+        <v>27215.9838724266</v>
       </c>
       <c r="F34" s="17" t="n">
-        <f aca="false">MAX(0,F22)*Premissas!$D$25</f>
-        <v>25858.9569690963</v>
+        <f aca="false">MAX(0,F22)*Premissas!$D$26</f>
+        <v>29383.8554692766</v>
       </c>
       <c r="G34" s="17" t="n">
-        <f aca="false">MAX(0,G22)*Premissas!$D$25</f>
-        <v>28139.0169881074</v>
+        <f aca="false">MAX(0,G22)*Premissas!$D$26</f>
+        <v>31733.8145639365</v>
       </c>
       <c r="H34" s="17" t="n">
-        <f aca="false">MAX(0,H22)*Premissas!$D$25</f>
-        <v>30609.2500678516</v>
+        <f aca="false">MAX(0,H22)*Premissas!$D$26</f>
+        <v>34275.3328247099</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>292</v>
@@ -19998,23 +20055,23 @@
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">FCFF!D22-D34</f>
-        <v>-3775.87335293162</v>
+        <v>-2173.63831146962</v>
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">FCFF!E22-E34</f>
-        <v>-3179.81441066505</v>
+        <v>-1545.8068945163</v>
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">FCFF!F22-F34</f>
-        <v>-2307.54764246958</v>
+        <v>-641.137600410879</v>
       </c>
       <c r="G35" s="17" t="n">
         <f aca="false">FCFF!G22-G34</f>
-        <v>-1372.01261747316</v>
+        <v>327.442495694937</v>
       </c>
       <c r="H35" s="17" t="n">
         <f aca="false">FCFF!H22-H34</f>
-        <v>-342.910192445892</v>
+        <v>1390.24527876402</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>294</v>
@@ -20041,23 +20098,23 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">C38+D35</f>
-        <v>37853.1266470684</v>
+        <v>39455.3616885304</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">D38+E35</f>
-        <v>34673.3122364033</v>
+        <v>37909.5547940141</v>
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">E38+F35</f>
-        <v>32365.7645939337</v>
+        <v>37268.4171936032</v>
       </c>
       <c r="G38" s="17" t="n">
         <f aca="false">F38+G35</f>
-        <v>30993.7519764606</v>
+        <v>37595.8596892981</v>
       </c>
       <c r="H38" s="17" t="n">
         <f aca="false">G38+H35</f>
-        <v>30650.8417840147</v>
+        <v>38986.1049680622</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>296</v>
@@ -20137,23 +20194,23 @@
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">D38+D27+D28+D26+D39+D40</f>
-        <v>486759.108466257</v>
+        <v>488361.343507719</v>
       </c>
       <c r="E41" s="31" t="n">
         <f aca="false">E38+E27+E28+E26+E39+E40</f>
-        <v>498582.970702309</v>
+        <v>501819.213259919</v>
       </c>
       <c r="F41" s="31" t="n">
         <f aca="false">F38+F27+F28+F26+F39+F40</f>
-        <v>511399.195549969</v>
+        <v>516301.848149639</v>
       </c>
       <c r="G41" s="31" t="n">
         <f aca="false">G38+G27+G28+G26+G39+G40</f>
-        <v>525292.370112162</v>
+        <v>531894.477824999</v>
       </c>
       <c r="H41" s="31" t="n">
         <f aca="false">H38+H27+H28+H26+H39+H40</f>
-        <v>540351.482186252</v>
+        <v>548686.745370299</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>300</v>
@@ -20233,23 +20290,23 @@
       </c>
       <c r="D44" s="17" t="n">
         <f aca="false">C44+D22-D34</f>
-        <v>199242.907414596</v>
+        <v>200845.142456058</v>
       </c>
       <c r="E44" s="17" t="n">
         <f aca="false">D44+E22-E34</f>
-        <v>210475.366500875</v>
+        <v>213711.609058486</v>
       </c>
       <c r="F44" s="17" t="n">
         <f aca="false">E44+F22-F34</f>
-        <v>222700.293138696</v>
+        <v>227602.945738365</v>
       </c>
       <c r="G44" s="17" t="n">
         <f aca="false">F44+G22-G34</f>
-        <v>236003.127384914</v>
+        <v>242605.235097752</v>
       </c>
       <c r="H44" s="17" t="n">
         <f aca="false">G44+H22-H34</f>
-        <v>250473.774324208</v>
+        <v>258809.037508255</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>304</v>
@@ -20265,23 +20322,23 @@
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">D29+D42+D43+D44</f>
-        <v>486759.108466257</v>
+        <v>488361.343507719</v>
       </c>
       <c r="E45" s="31" t="n">
         <f aca="false">E29+E42+E43+E44</f>
-        <v>498582.970702309</v>
+        <v>501819.213259919</v>
       </c>
       <c r="F45" s="31" t="n">
         <f aca="false">F29+F42+F43+F44</f>
-        <v>511399.195549969</v>
+        <v>516301.848149639</v>
       </c>
       <c r="G45" s="31" t="n">
         <f aca="false">G29+G42+G43+G44</f>
-        <v>525292.370112162</v>
+        <v>531894.477824999</v>
       </c>
       <c r="H45" s="31" t="n">
         <f aca="false">H29+H42+H43+H44</f>
-        <v>540351.482186252</v>
+        <v>548686.745370299</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>306</v>
@@ -20372,23 +20429,23 @@
       </c>
       <c r="D50" s="17" t="n">
         <f aca="false">D42-D38</f>
-        <v>65603.8733529316</v>
+        <v>64001.6383114696</v>
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">E42-E38</f>
-        <v>68783.6877635967</v>
+        <v>65547.4452059859</v>
       </c>
       <c r="F50" s="17" t="n">
         <f aca="false">F42-F38</f>
-        <v>71091.2354060663</v>
+        <v>66188.5828063968</v>
       </c>
       <c r="G50" s="17" t="n">
         <f aca="false">G42-G38</f>
-        <v>72463.2480235394</v>
+        <v>65861.1403107019</v>
       </c>
       <c r="H50" s="17" t="n">
         <f aca="false">H42-H38</f>
-        <v>72806.1582159853</v>
+        <v>64470.8950319378</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>311</v>
@@ -20404,23 +20461,23 @@
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">D50/D14</f>
-        <v>0.869770419747543</v>
+        <v>0.848528127588214</v>
       </c>
       <c r="E51" s="29" t="n">
         <f aca="false">E50/E14</f>
-        <v>0.849428491618565</v>
+        <v>0.809463250969197</v>
       </c>
       <c r="F51" s="29" t="n">
         <f aca="false">F50/F14</f>
-        <v>0.81866506859287</v>
+        <v>0.762207610737904</v>
       </c>
       <c r="G51" s="29" t="n">
         <f aca="false">G50/G14</f>
-        <v>0.778948593031553</v>
+        <v>0.707978788969127</v>
       </c>
       <c r="H51" s="29" t="n">
         <f aca="false">H50/H14</f>
-        <v>0.731280636486909</v>
+        <v>0.647559468993994</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>312</v>
@@ -20766,23 +20823,23 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">Projeção!D22</f>
-        <v>32139.898487837</v>
+        <v>37131.284909837</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">Projeção!E22</f>
-        <v>34992.0843809337</v>
+        <v>40082.4504748551</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">Projeção!F22</f>
-        <v>38083.8836069165</v>
+        <v>43275.1921491555</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">Projeção!G22</f>
-        <v>41441.8512343261</v>
+        <v>46736.1039233233</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">Projeção!H22</f>
-        <v>45079.8970071452</v>
+        <v>50479.1352352134</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>333</v>
@@ -20934,23 +20991,23 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D16-D17+D18-D19-D20+D21</f>
-        <v>18047.1177203097</v>
+        <v>23038.5041423097</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">E16-E17+E18-E19-E20+E21</f>
-        <v>20579.8108839889</v>
+        <v>25670.1769779103</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">F16-F17+F18-F19-F20+F21</f>
-        <v>23551.4093266267</v>
+        <v>28742.7178688657</v>
       </c>
       <c r="G22" s="31" t="n">
         <f aca="false">G16-G17+G18-G19-G20+G21</f>
-        <v>26767.0043706343</v>
+        <v>32061.2570596314</v>
       </c>
       <c r="H22" s="31" t="n">
         <f aca="false">H16-H17+H18-H19-H20+H21</f>
-        <v>30266.3398754057</v>
+        <v>35665.578103474</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>337</v>
@@ -20972,7 +21029,7 @@
         <v>339</v>
       </c>
       <c r="D25" s="17" t="n">
-        <f aca="false">Premissas!$D$32*H10</f>
+        <f aca="false">Premissas!$D$33*H10</f>
         <v>19992.8602378074</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -20997,7 +21054,7 @@
       </c>
       <c r="D27" s="17" t="n">
         <f aca="false">H16-H17+H18-D25-H20+H21</f>
-        <v>46065.4322105305</v>
+        <v>51464.6704385988</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>344</v>
@@ -21056,7 +21113,7 @@
         <v>347</v>
       </c>
       <c r="D5" s="18" t="n">
-        <f aca="false">Premissas!$D$26</f>
+        <f aca="false">Premissas!$D$27</f>
         <v>0.1291</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -21068,7 +21125,7 @@
         <v>349</v>
       </c>
       <c r="D6" s="30" t="n">
-        <f aca="false">Premissas!$D$27</f>
+        <f aca="false">Premissas!$D$28</f>
         <v>0.7558</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -21080,7 +21137,7 @@
         <v>351</v>
       </c>
       <c r="D7" s="18" t="n">
-        <f aca="false">Premissas!$D$28</f>
+        <f aca="false">Premissas!$D$29</f>
         <v>0.0423</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -21092,7 +21149,7 @@
         <v>353</v>
       </c>
       <c r="D8" s="18" t="n">
-        <f aca="false">Premissas!$D$29</f>
+        <f aca="false">Premissas!$D$30</f>
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -21128,8 +21185,8 @@
         <v>358</v>
       </c>
       <c r="D12" s="18" t="n">
-        <f aca="false">Premissas!$D$23</f>
-        <v>0.1291</v>
+        <f aca="false">Premissas!$D$24</f>
+        <v>0.0715</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>359</v>
@@ -21153,7 +21210,7 @@
       </c>
       <c r="D14" s="32" t="n">
         <f aca="false">D12*(1-D13)</f>
-        <v>0.085206</v>
+        <v>0.04719</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>363</v>
@@ -21176,7 +21233,7 @@
         <v>69</v>
       </c>
       <c r="D17" s="18" t="n">
-        <f aca="false">Premissas!$D$30</f>
+        <f aca="false">Premissas!$D$31</f>
         <v>0.2625</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -21201,7 +21258,7 @@
       </c>
       <c r="D19" s="32" t="n">
         <f aca="false">D9*D18+D14*D17</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>369</v>
@@ -21225,7 +21282,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">Painel!$C$12</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>372</v>
@@ -21272,7 +21329,7 @@
         <v>378</v>
       </c>
       <c r="D27" s="17" t="n">
-        <f aca="false">Premissas!$D$39</f>
+        <f aca="false">Premissas!$D$40</f>
         <v>275454.8362</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -21407,7 +21464,7 @@
         <v>388</v>
       </c>
       <c r="D7" s="33" t="n">
-        <f aca="false">(DATE(2026,12,31)-Premissas!$D$36)/365</f>
+        <f aca="false">(DATE(2026,12,31)-Premissas!$D$37)/365</f>
         <v>0.504109589041096</v>
       </c>
       <c r="E7" s="33" t="n">
@@ -21488,23 +21545,23 @@
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^D9</f>
-        <v>0.967265990340734</v>
+        <v>0.969409760890913</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^E9</f>
-        <v>0.875829030426722</v>
+        <v>0.883587455256839</v>
       </c>
       <c r="F10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^F9</f>
-        <v>0.767492847801479</v>
+        <v>0.781122361886414</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^G9</f>
-        <v>0.672557372458218</v>
+        <v>0.690539618471215</v>
       </c>
       <c r="H10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^H9</f>
-        <v>0.589364996095576</v>
+        <v>0.610461289991479</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>395</v>
@@ -21516,23 +21573,23 @@
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">D6*D7*D10</f>
-        <v>11844.2932210772</v>
+        <v>11870.5439600142</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">E6*E7*E10</f>
-        <v>23696.9148208663</v>
+        <v>23906.8310556065</v>
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">F6*F7*F10</f>
-        <v>23197.1550654883</v>
+        <v>23609.1015124177</v>
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">G6*G7*G10</f>
-        <v>22586.3153652864</v>
+        <v>23190.2083505662</v>
       </c>
       <c r="H11" s="31" t="n">
         <f aca="false">H6*H7*H10</f>
-        <v>21904.8268469746</v>
+        <v>22688.9091524458</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>397</v>
@@ -21555,7 +21612,7 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">WACC!$D$22</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>400</v>
@@ -21566,7 +21623,7 @@
         <v>401</v>
       </c>
       <c r="D15" s="18" t="n">
-        <f aca="false">Premissas!$D$31</f>
+        <f aca="false">Premissas!$D$32</f>
         <v>0.035</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -21591,7 +21648,7 @@
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">D16*(1+D15)/(D14-D15)</f>
-        <v>516407.475225762</v>
+        <v>569989.379756602</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>405</v>
@@ -21603,7 +21660,7 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D17/(1+D14)^H8</f>
-        <v>284907.812990989</v>
+        <v>327159.592579581</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>407</v>
@@ -21626,7 +21683,7 @@
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">SUM($D$11:$H$11)</f>
-        <v>103229.505319693</v>
+        <v>105265.59403105</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>409</v>
@@ -21638,7 +21695,7 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D21+D18</f>
-        <v>388137.318310682</v>
+        <v>432425.186610631</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>411</v>
@@ -21685,7 +21742,7 @@
         <v>418</v>
       </c>
       <c r="D26" s="17" t="n">
-        <f aca="false">Premissas!$D$33</f>
+        <f aca="false">Premissas!$D$34</f>
         <v>0</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -21698,7 +21755,7 @@
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">D22-D23-D24+D25-D26</f>
-        <v>342361.318310682</v>
+        <v>386649.186610631</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>421</v>
@@ -21709,7 +21766,7 @@
         <v>422</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">Premissas!$D$37</f>
+        <f aca="false">Premissas!$D$38</f>
         <v>4072.366</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -21722,7 +21779,7 @@
       </c>
       <c r="D29" s="25" t="n">
         <f aca="false">D27/D28</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>424</v>
@@ -21733,7 +21790,7 @@
         <v>26</v>
       </c>
       <c r="D30" s="16" t="n">
-        <f aca="false">Premissas!$D$38</f>
+        <f aca="false">Premissas!$D$39</f>
         <v>67.64</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -21746,7 +21803,7 @@
       </c>
       <c r="D31" s="11" t="n">
         <f aca="false">D29/D30-1</f>
-        <v>0.242894562985227</v>
+        <v>0.403675433288633</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>29</v>
@@ -21758,7 +21815,7 @@
       </c>
       <c r="D32" s="11" t="n">
         <f aca="false">D18/D22</f>
-        <v>0.734038701125195</v>
+        <v>0.756569234886324</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>427</v>
@@ -21770,7 +21827,7 @@
       </c>
       <c r="D33" s="29" t="n">
         <f aca="false">D22/Projeção!D14</f>
-        <v>5.14589064658759</v>
+        <v>5.73305533416239</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>429</v>
@@ -21793,23 +21850,23 @@
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">FCFF!D22</f>
-        <v>18047.1177203097</v>
+        <v>23038.5041423097</v>
       </c>
       <c r="E36" s="31" t="n">
         <f aca="false">FCFF!E22</f>
-        <v>20579.8108839889</v>
+        <v>25670.1769779103</v>
       </c>
       <c r="F36" s="31" t="n">
         <f aca="false">FCFF!F22</f>
-        <v>23551.4093266267</v>
+        <v>28742.7178688657</v>
       </c>
       <c r="G36" s="31" t="n">
         <f aca="false">FCFF!G22</f>
-        <v>26767.0043706343</v>
+        <v>32061.2570596314</v>
       </c>
       <c r="H36" s="31" t="n">
         <f aca="false">FCFF!H22</f>
-        <v>30266.3398754057</v>
+        <v>35665.578103474</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>432</v>
@@ -21849,23 +21906,23 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">D36*D7*D37</f>
-        <v>8761.62993790941</v>
+        <v>11184.8800870152</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">E36*E7*E37</f>
-        <v>17713.9863896116</v>
+        <v>22095.4977754143</v>
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">F36*F7*F37</f>
-        <v>17459.5600779558</v>
+        <v>21308.0755582567</v>
       </c>
       <c r="G38" s="17" t="n">
         <f aca="false">G36*G7*G37</f>
-        <v>17090.6127984398</v>
+        <v>20470.9695059695</v>
       </c>
       <c r="H38" s="17" t="n">
         <f aca="false">H36*H7*H37</f>
-        <v>16644.0587024557</v>
+        <v>19613.2065540443</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>436</v>
@@ -21889,7 +21946,7 @@
       </c>
       <c r="D40" s="17" t="n">
         <f aca="false">FCFF!D27</f>
-        <v>46065.4322105305</v>
+        <v>51464.6704385988</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>439</v>
@@ -21901,7 +21958,7 @@
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">D40*(1+D15)/(D39-D15)/(1+D39)^H8</f>
-        <v>193006.815285186</v>
+        <v>215628.762488522</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>441</v>
@@ -21913,7 +21970,7 @@
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">SUM($D$38:$H$38)+D41-D24+D25-D26</f>
-        <v>293092.663191558</v>
+        <v>332717.391969222</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>443</v>
@@ -21925,7 +21982,7 @@
       </c>
       <c r="D43" s="16" t="n">
         <f aca="false">D42/D28</f>
-        <v>71.9711006308269</v>
+        <v>81.7012498309882</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>445</v>
@@ -21973,131 +22030,131 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="34" t="n">
         <f aca="false">$D$14+-2*0.01</f>
-        <v>0.12115595075</v>
+        <v>0.11117675075</v>
       </c>
       <c r="D47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+D$46)/($C47-D$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>97.9596452787297</v>
+        <v>111.885663287535</v>
       </c>
       <c r="E47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+E$46)/($C47-E$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>102.92926692267</v>
+        <v>118.310598845127</v>
       </c>
       <c r="F47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+F$46)/($C47-F$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>108.475705559596</v>
+        <v>125.578959134587</v>
       </c>
       <c r="G47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+G$46)/($C47-G$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>114.705573887834</v>
+        <v>133.868489990682</v>
       </c>
       <c r="H47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+H$46)/($C47-H$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>121.753483126453</v>
+        <v>143.410655761932</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="34" t="n">
         <f aca="false">$D$14+-1*0.01</f>
-        <v>0.13115595075</v>
+        <v>0.12117675075</v>
       </c>
       <c r="D48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+D$46)/($C48-D$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>86.6963661597229</v>
+        <v>97.933713472542</v>
       </c>
       <c r="E48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+E$46)/($C48-E$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>90.6285633105005</v>
+        <v>102.900803963437</v>
       </c>
       <c r="F48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+F$46)/($C48-F$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>94.9697000141717</v>
+        <v>108.444278507765</v>
       </c>
       <c r="G48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+G$46)/($C48-G$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>99.7870685675417</v>
+        <v>114.670642486951</v>
       </c>
       <c r="H48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+H$46)/($C48-H$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>105.163582311863</v>
+        <v>121.714363982424</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="34" t="n">
         <f aca="false">$D$14+0*0.01</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="D49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+D$46)/($C49-D$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>77.4285830281698</v>
+        <v>86.6752149546068</v>
       </c>
       <c r="E49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+E$46)/($C49-E$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>80.5996277913376</v>
+        <v>90.6055803059333</v>
       </c>
       <c r="F49" s="25" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+F$46)/($C49-F$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
       <c r="G49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+G$46)/($C49-G$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>87.882159695899</v>
+        <v>99.7595240214417</v>
       </c>
       <c r="H49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+H$46)/($C49-H$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>92.0914507039167</v>
+        <v>105.133167571605</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="34" t="n">
         <f aca="false">$D$14+1*0.01</f>
-        <v>0.15115595075</v>
+        <v>0.14117675075</v>
       </c>
       <c r="D50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+D$46)/($C50-D$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>69.6786574917499</v>
+        <v>77.4110248998399</v>
       </c>
       <c r="E50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+E$46)/($C50-E$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>72.2767009953681</v>
+        <v>80.5807063123081</v>
       </c>
       <c r="F50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+F$46)/($C50-F$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>75.0984130658433</v>
+        <v>84.0489164883783</v>
       </c>
       <c r="G50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+G$46)/($C50-G$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>78.1739767791174</v>
+        <v>87.8599139303333</v>
       </c>
       <c r="H50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+H$46)/($C50-H$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>81.5392617648727</v>
+        <v>92.067160716567</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C51" s="34" t="n">
         <f aca="false">$D$14+2*0.01</f>
-        <v>0.16115595075</v>
+        <v>0.15117675075</v>
       </c>
       <c r="D51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+D$46)/($C51-D$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>63.1094664363626</v>
+        <v>69.6638664549153</v>
       </c>
       <c r="E51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+E$46)/($C51-E$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>65.2667711026161</v>
+        <v>72.2608713618896</v>
       </c>
       <c r="F51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+F$46)/($C51-F$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>67.5950787737559</v>
+        <v>75.0814153926739</v>
       </c>
       <c r="G51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+G$46)/($C51-G$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>70.1155608826122</v>
+        <v>78.1556585117799</v>
       </c>
       <c r="H51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+H$46)/($C51-H$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>72.8530342082407</v>
+        <v>81.5194417700774</v>
       </c>
     </row>
   </sheetData>
@@ -22588,7 +22645,7 @@
       </c>
       <c r="C20" s="36" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>481</v>
@@ -22735,19 +22792,19 @@
       </c>
       <c r="E7" s="17" t="n">
         <f aca="false">Projeção!E17</f>
-        <v>3543.0526541656</v>
+        <v>3693.02185404644</v>
       </c>
       <c r="F7" s="17" t="n">
         <f aca="false">Projeção!F17</f>
-        <v>3245.42202532735</v>
+        <v>3548.33432871972</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">Projeção!G17</f>
-        <v>3029.4355659922</v>
+        <v>3488.32384932126</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">Projeção!H17</f>
-        <v>2901.01518499671</v>
+        <v>3518.97246691831</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>492</v>
@@ -22791,19 +22848,19 @@
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">E6+E7+E8</f>
-        <v>86089.483798512</v>
+        <v>86239.4529983928</v>
       </c>
       <c r="F9" s="31" t="n">
         <f aca="false">F6+F7+F8</f>
-        <v>91653.4198017057</v>
+        <v>91956.3321050981</v>
       </c>
       <c r="G9" s="31" t="n">
         <f aca="false">G6+G7+G8</f>
-        <v>97626.4320479079</v>
+        <v>98085.3203312369</v>
       </c>
       <c r="H9" s="31" t="n">
         <f aca="false">H6+H7+H8</f>
-        <v>104030.821069846</v>
+        <v>104648.778351767</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>496</v>
@@ -22826,23 +22883,23 @@
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Projeção!D21</f>
-        <v>17365.705281613</v>
+        <v>19937.025559613</v>
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">Projeção!E21</f>
-        <v>18835.0131659356</v>
+        <v>21457.322971895</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">Projeção!F21</f>
-        <v>20427.7582217449</v>
+        <v>23102.0686828983</v>
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">Projeção!G21</f>
-        <v>22157.6203328347</v>
+        <v>24884.9626271665</v>
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">Projeção!H21</f>
-        <v>24031.765124893</v>
+        <v>26813.1908787463</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>498</v>
@@ -22910,23 +22967,23 @@
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Projeção!D18</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">Projeção!E18</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="F14" s="17" t="n">
         <f aca="false">Projeção!F18</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">Projeção!G18</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">Projeção!H18</f>
-        <v>13356.2987</v>
+        <v>5793.592</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>503</v>
@@ -22966,23 +23023,23 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">Projeção!D34</f>
-        <v>21822.9910732413</v>
+        <v>25212.1424537793</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">Projeção!E34</f>
-        <v>23759.625294654</v>
+        <v>27215.9838724266</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">Projeção!F34</f>
-        <v>25858.9569690963</v>
+        <v>29383.8554692766</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">Projeção!G34</f>
-        <v>28139.0169881074</v>
+        <v>31733.8145639365</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">Projeção!H34</f>
-        <v>30609.2500678516</v>
+        <v>34275.3328247099</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>507</v>
@@ -22994,23 +23051,23 @@
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">SUM(D11:D16)</f>
-        <v>84669.0027223816</v>
+        <v>83066.7676809196</v>
       </c>
       <c r="E17" s="31" t="n">
         <f aca="false">SUM(E11:E16)</f>
-        <v>89269.298209177</v>
+        <v>87785.2598929091</v>
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">SUM(F11:F16)</f>
-        <v>93960.9674441753</v>
+        <v>92597.4697055089</v>
       </c>
       <c r="G17" s="31" t="n">
         <f aca="false">SUM(G11:G16)</f>
-        <v>98998.444665381</v>
+        <v>97757.877835542</v>
       </c>
       <c r="H17" s="31" t="n">
         <f aca="false">SUM(H11:H16)</f>
-        <v>104373.731262291</v>
+        <v>103258.533073003</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>509</v>
@@ -23033,23 +23090,23 @@
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">D9-D17</f>
-        <v>-3775.87335293161</v>
+        <v>-2173.63831146962</v>
       </c>
       <c r="E19" s="31" t="n">
         <f aca="false">E9-E17</f>
-        <v>-3179.81441066504</v>
+        <v>-1545.80689451631</v>
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">F9-F17</f>
-        <v>-2307.5476424696</v>
+        <v>-641.137600410861</v>
       </c>
       <c r="G19" s="31" t="n">
         <f aca="false">G9-G17</f>
-        <v>-1372.01261747316</v>
+        <v>327.442495694937</v>
       </c>
       <c r="H19" s="31" t="n">
         <f aca="false">H9-H17</f>
-        <v>-342.91019244591</v>
+        <v>1390.24527876402</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>512</v>
@@ -23061,23 +23118,23 @@
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">Projeção!D38</f>
-        <v>37853.1266470684</v>
+        <v>39455.3616885304</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">Projeção!E38</f>
-        <v>34673.3122364033</v>
+        <v>37909.5547940141</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">Projeção!F38</f>
-        <v>32365.7645939337</v>
+        <v>37268.4171936032</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">Projeção!G38</f>
-        <v>30993.7519764606</v>
+        <v>37595.8596892981</v>
       </c>
       <c r="H20" s="17" t="n">
         <f aca="false">Projeção!H38</f>
-        <v>30650.8417840147</v>
+        <v>38986.1049680622</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>514</v>
@@ -23093,11 +23150,11 @@
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">ROUND(E19-Projeção!E35,3)</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" s="17" t="n">
         <f aca="false">ROUND(F19-Projeção!F35,3)</f>
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G21" s="17" t="n">
         <f aca="false">ROUND(G19-Projeção!G35,3)</f>
@@ -23105,7 +23162,7 @@
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">ROUND(H19-Projeção!H35,3)</f>
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>516</v>
@@ -23132,15 +23189,15 @@
       </c>
       <c r="D25" s="41" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>51.0489960521451</v>
+        <v>56.9203936118611</v>
       </c>
       <c r="E25" s="41" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076432</v>
       </c>
       <c r="F25" s="41" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>138.611356353207</v>
+        <v>159.343024237654</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23149,15 +23206,15 @@
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>253666.19585689</v>
+        <v>277576.67565156</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>388137.318310682</v>
+        <v>432425.186610632</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>610252.174826684</v>
+        <v>694679.114242599</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23166,15 +23223,15 @@
       </c>
       <c r="D27" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>207890.19585689</v>
+        <v>231800.67565156</v>
       </c>
       <c r="E27" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>342361.318310682</v>
+        <v>386649.186610632</v>
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>564476.174826684</v>
+        <v>648903.114242599</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23183,15 +23240,15 @@
       </c>
       <c r="D28" s="11" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.15675595075</v>
+        <v>0.14677675075</v>
       </c>
       <c r="E28" s="11" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.12555595075</v>
+        <v>0.11557675075</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23251,15 +23308,15 @@
       </c>
       <c r="D32" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>32462.2701831158</v>
+        <v>40797.5333671632</v>
       </c>
       <c r="E32" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>30650.8417840147</v>
+        <v>38986.1049680622</v>
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>33287.5562690417</v>
+        <v>41622.8194530891</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23268,15 +23325,15 @@
       </c>
       <c r="D33" s="29" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.934487891463087</v>
+        <v>0.824772669815776</v>
       </c>
       <c r="E33" s="29" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.731280636486909</v>
+        <v>0.647559468993994</v>
       </c>
       <c r="F33" s="29" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.543943390811722</v>
+        <v>0.479329634758266</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23299,13 +23356,13 @@
         <v>24</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>51.0489960521451</v>
+        <v>56.9203936118611</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>84.0693882403208</v>
+        <v>94.9446063076432</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>138.611356353207</v>
+        <v>159.343024237654</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23313,13 +23370,13 @@
         <v>30</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>253666.19585689</v>
+        <v>277576.67565156</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>388137.318310682</v>
+        <v>432425.186610632</v>
       </c>
       <c r="F38" s="17" t="n">
-        <v>610252.174826684</v>
+        <v>694679.114242599</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23327,13 +23384,13 @@
         <v>32</v>
       </c>
       <c r="D39" s="17" t="n">
-        <v>207890.19585689</v>
+        <v>231800.67565156</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>342361.318310682</v>
+        <v>386649.186610632</v>
       </c>
       <c r="F39" s="17" t="n">
-        <v>564476.174826684</v>
+        <v>648903.114242599</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23341,13 +23398,13 @@
         <v>399</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.15675595075</v>
+        <v>0.14677675075</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.14115595075</v>
+        <v>0.13117675075</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.12555595075</v>
+        <v>0.11557675075</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23397,13 +23454,13 @@
         <v>520</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>32462.2701831158</v>
+        <v>40797.5333671632</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>30650.8417840147</v>
+        <v>38986.1049680622</v>
       </c>
       <c r="F44" s="17" t="n">
-        <v>33287.5562690417</v>
+        <v>41622.8194530891</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23411,13 +23468,13 @@
         <v>521</v>
       </c>
       <c r="D45" s="29" t="n">
-        <v>0.934487891463087</v>
+        <v>0.824772669815776</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>0.731280636486909</v>
+        <v>0.647559468993994</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>0.543943390811722</v>
+        <v>0.479329634758266</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23538,13 +23595,13 @@
         <v>520</v>
       </c>
       <c r="D56" s="17" t="n">
-        <v>-3687.46361135201</v>
+        <v>11626.8757892491</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>-1569.66014190046</v>
+        <v>11366.9708296553</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>3105.15012697354</v>
+        <v>13099.8580403209</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23552,13 +23609,13 @@
         <v>521</v>
       </c>
       <c r="D57" s="29" t="n">
-        <v>6.66167188649241</v>
+        <v>4.85959661759654</v>
       </c>
       <c r="E57" s="29" t="n">
-        <v>5.20220134324432</v>
+        <v>3.96722679187521</v>
       </c>
       <c r="F57" s="29" t="n">
-        <v>3.45344830762287</v>
+        <v>2.76062163176999</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23581,13 +23638,13 @@
         <v>24</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>11.4949241466429</v>
+        <v>11.9396986702007</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>21.3835729098938</v>
+        <v>22.3229527459937</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>40.8409931438173</v>
+        <v>42.8784481671766</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23595,13 +23652,13 @@
         <v>30</v>
       </c>
       <c r="D62" s="17" t="n">
-        <v>27173.5950831609</v>
+        <v>28046.7677991838</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>46586.798495389</v>
+        <v>48430.9707656516</v>
       </c>
       <c r="F62" s="17" t="n">
-        <v>84785.2284246752</v>
+        <v>88785.1205999066</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23609,13 +23666,13 @@
         <v>32</v>
       </c>
       <c r="D63" s="17" t="n">
-        <v>22566.6120831609</v>
+        <v>23439.7847991838</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>41979.815495389</v>
+        <v>43823.9877656516</v>
       </c>
       <c r="F63" s="17" t="n">
-        <v>80178.2454246751</v>
+        <v>84178.1375999066</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23623,13 +23680,13 @@
         <v>399</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>0.160612848641</v>
+        <v>0.156832395041</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.145012848641</v>
+        <v>0.141232395041</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>0.129412848641</v>
+        <v>0.125632395041</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23679,13 +23736,13 @@
         <v>520</v>
       </c>
       <c r="D68" s="17" t="n">
-        <v>11133.5419715542</v>
+        <v>12250.190935772</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>12136.9580127926</v>
+        <v>13253.6069770103</v>
       </c>
       <c r="F68" s="17" t="n">
-        <v>16436.5845311779</v>
+        <v>17553.2334953957</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23693,13 +23750,13 @@
         <v>521</v>
       </c>
       <c r="D69" s="29" t="n">
-        <v>0.271773210330905</v>
+        <v>0.172227722212721</v>
       </c>
       <c r="E69" s="29" t="n">
-        <v>0.128627042958816</v>
+        <v>0.0583983382894964</v>
       </c>
       <c r="F69" s="29" t="n">
-        <v>-0.102078460937666</v>
+        <v>-0.152639192091905</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23708,7 +23765,7 @@
       </c>
       <c r="D73" s="25" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>84.0693882403208</v>
+        <v>94.9446063076431</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/saida/valuation_vale_csn_gerdau.xlsx
+++ b/saida/valuation_vale_csn_gerdau.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="767">
   <si>
     <t xml:space="preserve">Valuation de Vale, CSN e Gerdau</t>
   </si>
@@ -847,7 +847,7 @@
     <t xml:space="preserve">(-) Juros da dívida</t>
   </si>
   <si>
-    <t xml:space="preserve">Dívida do início do ano × juros pagos sobre a dívida (aba Premissas).</t>
+    <t xml:space="preserve">Dívida do início do ano × custo da dívida.</t>
   </si>
   <si>
     <t xml:space="preserve">(+/-) Resultado financeiro</t>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">Custo da dívida antes do imposto (Kd)</t>
   </si>
   <si>
-    <t xml:space="preserve">O que a dívida custa à empresa, em reais. Vem do custo que ela divulga (aba Premissas).</t>
+    <t xml:space="preserve">O juro que a empresa paga para tomar dinheiro emprestado.</t>
   </si>
   <si>
     <t xml:space="preserve">Alíquota de IR e CSLL</t>
@@ -2203,12 +2203,6 @@
     <t xml:space="preserve">Iguais nos três cenários, gerais</t>
   </si>
   <si>
-    <t xml:space="preserve">Juros pagos sobre a dívida (% do saldo inicial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo da dívida no WACC, em reais, antes do imposto (Kd)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dividendos (% do lucro)</t>
   </si>
   <si>
@@ -2239,13 +2233,13 @@
     <t xml:space="preserve">De onde veio</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,8% ao ano).</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.8% ao ano).</t>
   </si>
   <si>
     <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Daí até 2030 em linha reta. Faixa: margem EBITDA de 2021 a 2025, sem perdas por recuperabilidade. Pessimista é o segundo pior ano, moderado a mediana e otimista o segundo melhor.</t>
   </si>
   <si>
-    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12,2% a 15,3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
+    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12.2% a 15.3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
   </si>
   <si>
     <t xml:space="preserve">Vendas, administrativas e outras, sem perdas por recuperabilidade. Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
@@ -2266,10 +2260,7 @@
     <t xml:space="preserve">Alíquota nominal: IRPJ 25% + CSLL 9%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo médio de 5,6% ao ano em dólar, depois de swaps (formulário 6-K do 2T26, SEC).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo médio de 5,6% ao ano em dólar, depois de swaps (formulário 6-K do 2T26, SEC). A parte em dólar foi trazida para reais pela diferença de inflação (3,5% no Brasil, 2,0% nos EUA).</t>
+    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 17.8%.</t>
   </si>
   <si>
     <t xml:space="preserve">Mediana 2023-2025 da receita financeira sobre o caixa médio.</t>
@@ -2281,7 +2272,7 @@
     <t xml:space="preserve">Tesouro prefixado de dez anos (em reais, nominal).</t>
   </si>
   <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,64.</t>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.64.</t>
   </si>
   <si>
     <t xml:space="preserve">Damodaran, mercado maduro. O risco-país já está no juro em reais.</t>
@@ -2320,28 +2311,22 @@
     <t xml:space="preserve">Pregão do preço acima.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10,0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A CSN não divulga custo médio. Juros pagos em 2025 (R$ 4.268 mi, linha "Juros pagos" do fluxo de caixa na CVM) sobre a dívida bruta média do ano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A empresa não divulga custo médio: mantido o piso, a taxa do Tesouro prefixado de dez anos, sem spread de crédito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1,48.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,1% ao ano).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53% da dívida em dólar a 6,13% ao ano e 46% em reais a CDI - 0,15% (formulário 6-K do 2T26, SEC). CDI de 13,65%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53% da dívida em dólar a 6,13% ao ano e 46% em reais a CDI - 0,15% (formulário 6-K do 2T26, SEC). CDI de 13,65%. A parte em dólar foi trazida para reais pela diferença de inflação (3,5% no Brasil, 2,0% nos EUA).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,71.</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10.0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 14.2%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1.48.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.1% ao ano).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 19.3%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.71.</t>
   </si>
   <si>
     <t xml:space="preserve">Dados da CVM</t>
@@ -3001,11 +2986,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="77798981"/>
-        <c:axId val="56045745"/>
+        <c:axId val="382606"/>
+        <c:axId val="86157532"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="77798981"/>
+        <c:axId val="382606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3037,7 +3022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56045745"/>
+        <c:crossAx val="86157532"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3045,7 +3030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56045745"/>
+        <c:axId val="86157532"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3087,7 +3072,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77798981"/>
+        <c:crossAx val="382606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4139,11 +4124,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="62519026"/>
-        <c:axId val="86150834"/>
+        <c:axId val="58037023"/>
+        <c:axId val="28988576"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="62519026"/>
+        <c:axId val="58037023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4175,7 +4160,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86150834"/>
+        <c:crossAx val="28988576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4183,7 +4168,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86150834"/>
+        <c:axId val="28988576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4225,7 +4210,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62519026"/>
+        <c:crossAx val="58037023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4805,11 +4790,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="98891909"/>
-        <c:axId val="50635579"/>
+        <c:axId val="94622550"/>
+        <c:axId val="19950160"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="98891909"/>
+        <c:axId val="94622550"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4851,12 +4836,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50635579"/>
+        <c:crossAx val="19950160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="50635579"/>
+        <c:axId val="19950160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4898,7 +4883,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98891909"/>
+        <c:crossAx val="94622550"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5370,24 +5355,24 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF(ISNUMBER(G12),MIN(MAX(G12,MIN(D12:F12)),MAX(D12:F12)),CHOOSE(Painel!$Y$9,D12,E12,F12))</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$D$9</f>
-        <v>0.14677675075</v>
+        <v>0.15675595075</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$E$9</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">WACC!$D$19+Premissas!$F$9</f>
-        <v>0.11557675075</v>
+        <v>0.12555595075</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="11" t="n">
         <f aca="false">WACC!$D$19</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5412,7 +5397,7 @@
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>25</v>
@@ -5436,7 +5421,7 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">'Valor justo'!D31</f>
-        <v>0.403675433288633</v>
+        <v>0.242894562985227</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>29</v>
@@ -5448,7 +5433,7 @@
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>432425.186610631</v>
+        <v>388137.318310682</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>31</v>
@@ -5460,7 +5445,7 @@
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>386649.186610631</v>
+        <v>342361.318310682</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>33</v>
@@ -5472,7 +5457,7 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">'Valor justo'!D32</f>
-        <v>0.756569234886324</v>
+        <v>0.734038701125195</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>35</v>
@@ -5484,7 +5469,7 @@
       </c>
       <c r="C22" s="16" t="n">
         <f aca="false">'Valor justo'!D43</f>
-        <v>81.7012498309882</v>
+        <v>71.9711006308269</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>37</v>
@@ -5519,7 +5504,7 @@
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">WACC!D22</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>43</v>
@@ -5531,7 +5516,7 @@
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>105265.59403105</v>
+        <v>103229.505319693</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>45</v>
@@ -5543,7 +5528,7 @@
       </c>
       <c r="C28" s="17" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>327159.592579581</v>
+        <v>284907.812990989</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>45</v>
@@ -5555,7 +5540,7 @@
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>432425.186610631</v>
+        <v>388137.318310682</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>45</v>
@@ -5567,7 +5552,7 @@
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>386649.186610631</v>
+        <v>342361.318310682</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>45</v>
@@ -5579,7 +5564,7 @@
       </c>
       <c r="C31" s="16" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>50</v>
@@ -10524,7 +10509,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L158"/>
+  <dimension ref="B1:L154"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -10586,19 +10571,19 @@
         <v>714</v>
       </c>
       <c r="C7" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(C$1:C$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0209</v>
       </c>
       <c r="D7" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0378</v>
       </c>
       <c r="F7" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0683</v>
       </c>
       <c r="L7" s="7" t="s">
@@ -10610,19 +10595,19 @@
         <v>18</v>
       </c>
       <c r="C8" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(C$1:C$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.3459</v>
       </c>
       <c r="D8" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.3484</v>
       </c>
       <c r="E8" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.3936</v>
       </c>
       <c r="F8" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.4542</v>
       </c>
     </row>
@@ -10631,15 +10616,15 @@
         <v>715</v>
       </c>
       <c r="D9" s="32" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0156</v>
       </c>
       <c r="E9" s="32" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="F9" s="32" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>-0.0156</v>
       </c>
     </row>
@@ -10670,23 +10655,23 @@
         <v>717</v>
       </c>
       <c r="D12" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.083</v>
       </c>
       <c r="E12" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0815</v>
       </c>
       <c r="F12" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.08</v>
       </c>
       <c r="G12" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0785</v>
       </c>
       <c r="H12" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.077</v>
       </c>
     </row>
@@ -10695,23 +10680,23 @@
         <v>718</v>
       </c>
       <c r="D13" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="E13" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="F13" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="G13" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
       <c r="H13" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>-1570</v>
       </c>
     </row>
@@ -10720,23 +10705,23 @@
         <v>719</v>
       </c>
       <c r="D14" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.146</v>
       </c>
       <c r="E14" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.1449</v>
       </c>
       <c r="F14" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.1438</v>
       </c>
       <c r="G14" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.1427</v>
       </c>
       <c r="H14" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.1415</v>
       </c>
     </row>
@@ -10745,23 +10730,23 @@
         <v>720</v>
       </c>
       <c r="D15" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="E15" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="F15" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="G15" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
       <c r="H15" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.0569</v>
       </c>
     </row>
@@ -10770,23 +10755,23 @@
         <v>219</v>
       </c>
       <c r="D16" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="E16" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="F16" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="G16" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
       <c r="H16" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>21.598</v>
       </c>
     </row>
@@ -10795,23 +10780,23 @@
         <v>221</v>
       </c>
       <c r="D17" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="E17" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="F17" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="G17" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
       <c r="H17" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>98.067</v>
       </c>
     </row>
@@ -10820,23 +10805,23 @@
         <v>223</v>
       </c>
       <c r="D18" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="E18" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="F18" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="G18" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
       <c r="H18" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>91.9277</v>
       </c>
     </row>
@@ -10845,23 +10830,23 @@
         <v>721</v>
       </c>
       <c r="D19" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="E19" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(E$1:E$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="F19" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(F$1:F$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="G19" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(G$1:G$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
       <c r="H19" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(H$1:H$157,ROW()+38*Painel!$Y$5)</f>
         <v>0</v>
       </c>
     </row>
@@ -10884,372 +10869,386 @@
         <v>360</v>
       </c>
       <c r="D22" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
         <v>0.34</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>723</v>
+        <v>358</v>
       </c>
       <c r="D23" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.056</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>724</v>
+        <v>491</v>
       </c>
       <c r="D24" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0715</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>491</v>
+        <v>723</v>
       </c>
       <c r="D25" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0936</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.679</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>725</v>
+        <v>347</v>
       </c>
       <c r="D26" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.679</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="D27" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1291</v>
+        <v>349</v>
+      </c>
+      <c r="D27" s="50" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.7558</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D28" s="50" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.7558</v>
+        <v>351</v>
+      </c>
+      <c r="D28" s="48" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>351</v>
+        <v>724</v>
       </c>
       <c r="D29" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0423</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D30" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.2625</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>727</v>
+        <v>401</v>
       </c>
       <c r="D31" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.2625</v>
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0.035</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="D32" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0.035</v>
+        <v>726</v>
+      </c>
+      <c r="D32" s="51" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="D33" s="51" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="C35" s="9"/>
+      <c r="D35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="D34" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8"/>
+      <c r="D36" s="52" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>46203</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D37" s="52" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>46203</v>
+        <v>422</v>
+      </c>
+      <c r="D37" s="53" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>4072.366</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D38" s="53" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>4072.366</v>
+        <v>730</v>
+      </c>
+      <c r="D38" s="41" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>67.64</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D39" s="41" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>67.64</v>
+        <v>378</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>275454.8362</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D40" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>275454.8362</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="D40" s="54" t="str">
+        <f aca="false">INDEX(D$1:D$157,ROW()+38*Painel!$Y$5)</f>
+        <v>2026-10-08</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="D41" s="54" t="str">
-        <f aca="false">INDEX(D$1:D$161,ROW()+39*Painel!$Y$5)</f>
-        <v>2026-10-08</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="47" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>714</v>
+        <v>18</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0.0209</v>
+        <v>0.3459</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0</v>
+        <v>0.3484</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.0378</v>
+        <v>0.3936</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.0683</v>
+        <v>0.4542</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <v>0.3459</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>0.3484</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>0.3936</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>0.4542</v>
+        <v>715</v>
+      </c>
+      <c r="D47" s="55" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E47" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="55" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="I47" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="0" t="s">
+        <v>717</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>736</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="D48" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E48" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="E51" s="12" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>0.0785</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>0.077</v>
+        <v>718</v>
+      </c>
+      <c r="D51" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="E51" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="F51" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="G51" s="56" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="H51" s="56" t="n">
+        <v>-1570</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="E52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="F52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="G52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="H52" s="56" t="n">
-        <v>-1570</v>
+        <v>719</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>0.1415</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.146</v>
+        <v>0.0569</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.1449</v>
+        <v>0.0569</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.1438</v>
+        <v>0.0569</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.1427</v>
+        <v>0.0569</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0.1415</v>
+        <v>0.0569</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>0.0569</v>
+        <v>219</v>
+      </c>
+      <c r="D54" s="57" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="E54" s="57" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="F54" s="57" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="G54" s="57" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="H54" s="57" t="n">
+        <v>21.598</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>739</v>
@@ -11257,452 +11256,464 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D55" s="57" t="n">
-        <v>21.598</v>
+        <v>98.067</v>
       </c>
       <c r="E55" s="57" t="n">
-        <v>21.598</v>
+        <v>98.067</v>
       </c>
       <c r="F55" s="57" t="n">
-        <v>21.598</v>
+        <v>98.067</v>
       </c>
       <c r="G55" s="57" t="n">
-        <v>21.598</v>
+        <v>98.067</v>
       </c>
       <c r="H55" s="57" t="n">
-        <v>21.598</v>
+        <v>98.067</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D56" s="57" t="n">
-        <v>98.067</v>
+        <v>91.9277</v>
       </c>
       <c r="E56" s="57" t="n">
-        <v>98.067</v>
+        <v>91.9277</v>
       </c>
       <c r="F56" s="57" t="n">
-        <v>98.067</v>
+        <v>91.9277</v>
       </c>
       <c r="G56" s="57" t="n">
-        <v>98.067</v>
+        <v>91.9277</v>
       </c>
       <c r="H56" s="57" t="n">
-        <v>98.067</v>
+        <v>91.9277</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="D57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="E57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="F57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="G57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="H57" s="57" t="n">
-        <v>91.9277</v>
+        <v>721</v>
+      </c>
+      <c r="D57" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I57" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>741</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="D58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.34</v>
+        <v>0.1291</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>723</v>
+        <v>491</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.056</v>
+        <v>0.0936</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>0.0715</v>
+        <v>0.679</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>491</v>
+        <v>347</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.0936</v>
+        <v>0.1291</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>0.679</v>
+        <v>349</v>
+      </c>
+      <c r="D65" s="58" t="n">
+        <v>0.7558</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.1291</v>
+        <v>0.0423</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D67" s="58" t="n">
-        <v>0.7558</v>
+        <v>724</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>351</v>
+        <v>725</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>0.0423</v>
+        <v>0.2625</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>726</v>
+        <v>401</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="D70" s="12" t="n">
-        <v>0.2625</v>
+        <v>726</v>
+      </c>
+      <c r="D70" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="D71" s="12" t="n">
-        <v>0.035</v>
+        <v>727</v>
+      </c>
+      <c r="D71" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I71" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="D74" s="60" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I74" s="2" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D72" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" s="2" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="D75" s="61" t="n">
+        <v>4072.366</v>
+      </c>
+      <c r="I75" s="2" t="s">
         <v>754</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D73" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D76" s="60" t="n">
-        <v>46203</v>
+        <v>730</v>
+      </c>
+      <c r="D76" s="62" t="n">
+        <v>67.64</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D77" s="61" t="n">
-        <v>4072.366</v>
+        <v>378</v>
+      </c>
+      <c r="D77" s="56" t="n">
+        <v>275454.8362</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D78" s="62" t="n">
-        <v>67.64</v>
+        <v>731</v>
+      </c>
+      <c r="D78" s="63" t="s">
+        <v>757</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D79" s="56" t="n">
-        <v>275454.8362</v>
-      </c>
-      <c r="I79" s="2" t="s">
+    <row r="81" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>0.0778</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="D80" s="63" t="s">
-        <v>760</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="47" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="8" t="s">
+      <c r="B84" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="I84" s="2" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="C85" s="12" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="D85" s="12" t="n">
+        <v>715</v>
+      </c>
+      <c r="D85" s="55" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E85" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>0.0778</v>
+      <c r="F85" s="55" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C86" s="12" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="0" t="s">
+        <v>717</v>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="G88" s="12" t="n">
         <v>0.1713</v>
       </c>
-      <c r="D86" s="12" t="n">
-        <v>0.1884</v>
-      </c>
-      <c r="E86" s="12" t="n">
-        <v>0.2002</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="I86" s="2" t="s">
+      <c r="H88" s="12" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="I88" s="2" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="D87" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E87" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I87" s="2" t="s">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="D89" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="E89" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="F89" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="G89" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="H89" s="56" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="I89" s="2" t="s">
         <v>737</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>0.2146</v>
+        <v>0.1326</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0.2001</v>
+        <v>0.1237</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0.1857</v>
+        <v>0.1148</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.1713</v>
+        <v>0.1059</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0.1569</v>
+        <v>0.097</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>738</v>
@@ -11710,68 +11721,68 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="E91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="F91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="G91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="H91" s="56" t="n">
-        <v>351.131</v>
+        <v>720</v>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>0.0983</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="0" t="s">
-        <v>719</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>0.1326</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>0.1237</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>0.1148</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>0.1059</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>0.097</v>
+        <v>219</v>
+      </c>
+      <c r="D92" s="57" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="E92" s="57" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="F92" s="57" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="G92" s="57" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="H92" s="57" t="n">
+        <v>19.5303</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>0.0983</v>
+        <v>221</v>
+      </c>
+      <c r="D93" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="E93" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="F93" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="G93" s="57" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="H93" s="57" t="n">
+        <v>135.0709</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>739</v>
@@ -11779,118 +11790,94 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="0" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D94" s="57" t="n">
-        <v>19.5303</v>
+        <v>92.5353</v>
       </c>
       <c r="E94" s="57" t="n">
-        <v>19.5303</v>
+        <v>92.5353</v>
       </c>
       <c r="F94" s="57" t="n">
-        <v>19.5303</v>
+        <v>92.5353</v>
       </c>
       <c r="G94" s="57" t="n">
-        <v>19.5303</v>
+        <v>92.5353</v>
       </c>
       <c r="H94" s="57" t="n">
-        <v>19.5303</v>
+        <v>92.5353</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="D95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="E95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="F95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="G95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="H95" s="57" t="n">
-        <v>135.0709</v>
+        <v>721</v>
+      </c>
+      <c r="D95" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I95" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="D96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="E96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="F96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="G96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="H96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="D97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="8" t="s">
-        <v>734</v>
+      <c r="B99" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="0" t="s">
-        <v>360</v>
+        <v>491</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>0.34</v>
+        <v>0.0772</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>743</v>
@@ -11901,40 +11888,40 @@
         <v>723</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>0.0777</v>
+        <v>0.242</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="0" t="s">
-        <v>724</v>
+        <v>347</v>
       </c>
       <c r="D102" s="12" t="n">
         <v>0.1291</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="0" t="s">
-        <v>491</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>0.0772</v>
+        <v>349</v>
+      </c>
+      <c r="D103" s="58" t="n">
+        <v>1.483</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="0" t="s">
-        <v>725</v>
+        <v>351</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.242</v>
+        <v>0.0423</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>747</v>
@@ -11942,10 +11929,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="0" t="s">
-        <v>347</v>
+        <v>724</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>0.1291</v>
+        <v>0</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>748</v>
@@ -11953,21 +11940,21 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D106" s="58" t="n">
-        <v>1.483</v>
+        <v>725</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>0.8635</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.0423</v>
+        <v>0.035</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>750</v>
@@ -11977,8 +11964,8 @@
       <c r="B108" s="0" t="s">
         <v>726</v>
       </c>
-      <c r="D108" s="12" t="n">
-        <v>0</v>
+      <c r="D108" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>751</v>
@@ -11988,68 +11975,68 @@
       <c r="B109" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="D109" s="12" t="n">
-        <v>0.8635</v>
+      <c r="D109" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="D111" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>754</v>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
+      <c r="I111" s="8" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="D112" s="56" t="n">
-        <v>0</v>
+      <c r="D112" s="60" t="n">
+        <v>46203</v>
       </c>
       <c r="I112" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="D113" s="61" t="n">
+        <v>1326.0939</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="D114" s="62" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I114" s="2" t="s">
         <v>755</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="8" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D115" s="60" t="n">
-        <v>46203</v>
+        <v>378</v>
+      </c>
+      <c r="D115" s="56" t="n">
+        <v>8433.9575</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>756</v>
@@ -12057,197 +12044,233 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D116" s="61" t="n">
-        <v>1326.0939</v>
+        <v>731</v>
+      </c>
+      <c r="D116" s="63" t="s">
+        <v>757</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="0" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
+      <c r="I120" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="D117" s="62" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D118" s="56" t="n">
-        <v>8433.9575</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="D119" s="63" t="s">
-        <v>760</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="47" t="s">
-        <v>10</v>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="C123" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="8" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>-0.0045</v>
-      </c>
-      <c r="D124" s="12" t="n">
+      <c r="B123" s="0" t="s">
+        <v>715</v>
+      </c>
+      <c r="D123" s="55" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E123" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>766</v>
+      <c r="F123" s="55" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C125" s="12" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="D125" s="12" t="n">
-        <v>0.1613</v>
-      </c>
-      <c r="E125" s="12" t="n">
-        <v>0.1971</v>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>0.2506</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>736</v>
+      <c r="B125" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="D126" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E126" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="55" t="n">
-        <v>-0.0156</v>
+        <v>717</v>
+      </c>
+      <c r="D126" s="12" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>0.0261</v>
       </c>
       <c r="I126" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="D127" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="E127" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="F127" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="G127" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="H127" s="56" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="I127" s="2" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I128" s="8" t="s">
-        <v>734</v>
+      <c r="B128" s="0" t="s">
+        <v>719</v>
+      </c>
+      <c r="D128" s="12" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>0.0773</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="0" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>0.0332</v>
+        <v>0.0887</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>0.0315</v>
+        <v>0.0887</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>0.0297</v>
+        <v>0.0887</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.0279</v>
+        <v>0.0887</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0.0261</v>
+        <v>0.0887</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="D130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="E130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="F130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="G130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="H130" s="56" t="n">
-        <v>563.158</v>
+        <v>219</v>
+      </c>
+      <c r="D130" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="E130" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="F130" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="G130" s="57" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="H130" s="57" t="n">
+        <v>25.1348</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>739</v>
@@ -12255,45 +12278,45 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="0" t="s">
-        <v>719</v>
-      </c>
-      <c r="D131" s="12" t="n">
-        <v>0.0779</v>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v>0.0773</v>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>0.0767</v>
-      </c>
-      <c r="G131" s="12" t="n">
-        <v>0.0762</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>0.0756</v>
+        <v>221</v>
+      </c>
+      <c r="D131" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="E131" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="F131" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="G131" s="57" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="H131" s="57" t="n">
+        <v>92.3738</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>0.0887</v>
+        <v>223</v>
+      </c>
+      <c r="D132" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="E132" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="F132" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="G132" s="57" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="H132" s="57" t="n">
+        <v>31.414</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>739</v>
@@ -12301,324 +12324,244 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="E133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="F133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="G133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="H133" s="57" t="n">
-        <v>25.1348</v>
+        <v>721</v>
+      </c>
+      <c r="D133" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="D134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="E134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="F134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="G134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="H134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="D135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="E135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="F135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="G135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="H135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>741</v>
+      <c r="B135" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E135" s="9"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9"/>
+      <c r="I135" s="8" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="0" t="s">
-        <v>721</v>
-      </c>
-      <c r="D136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="56" t="n">
-        <v>0</v>
+        <v>360</v>
+      </c>
+      <c r="D136" s="12" t="n">
+        <v>0.34</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="D137" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="8" t="s">
-        <v>734</v>
+      <c r="B138" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="D138" s="12" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="0" t="s">
-        <v>360</v>
+        <v>723</v>
       </c>
       <c r="D139" s="12" t="n">
-        <v>0.34</v>
+        <v>0.3602</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="0" t="s">
-        <v>723</v>
+        <v>347</v>
       </c>
       <c r="D140" s="12" t="n">
-        <v>0.0955</v>
+        <v>0.1291</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>767</v>
+        <v>745</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="D141" s="12" t="n">
-        <v>0.1039</v>
+        <v>349</v>
+      </c>
+      <c r="D141" s="58" t="n">
+        <v>0.7921</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="0" t="s">
-        <v>491</v>
+        <v>351</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>0.1235</v>
+        <v>0.0423</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="0" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D143" s="12" t="n">
-        <v>0.3602</v>
+        <v>0</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="0" t="s">
-        <v>347</v>
+        <v>725</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>0.1291</v>
+        <v>0.2273</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D145" s="58" t="n">
-        <v>0.7921</v>
+        <v>401</v>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>0.035</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="D146" s="12" t="n">
-        <v>0.0423</v>
+        <v>726</v>
+      </c>
+      <c r="D146" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D147" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="D147" s="56" t="n">
         <v>0</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="D148" s="12" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="I148" s="2" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="D149" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I149" s="2" t="s">
-        <v>753</v>
+      <c r="B149" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="C149" s="9"/>
+      <c r="D149" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="9"/>
+      <c r="F149" s="9"/>
+      <c r="G149" s="9"/>
+      <c r="H149" s="9"/>
+      <c r="I149" s="8" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D150" s="59" t="n">
-        <v>1</v>
+        <v>729</v>
+      </c>
+      <c r="D150" s="60" t="n">
+        <v>46203</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D151" s="56" t="n">
-        <v>0</v>
+        <v>422</v>
+      </c>
+      <c r="D151" s="61" t="n">
+        <v>1963.1806</v>
       </c>
       <c r="I151" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="D152" s="62" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="I152" s="2" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
-      <c r="I153" s="8" t="s">
-        <v>734</v>
+      <c r="B153" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="D153" s="56" t="n">
+        <v>46089.0479</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="D154" s="60" t="n">
-        <v>46203</v>
+      <c r="D154" s="63" t="s">
+        <v>757</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="D155" s="61" t="n">
-        <v>1963.1806</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D156" s="62" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="I156" s="2" t="s">
         <v>758</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="D157" s="56" t="n">
-        <v>46089.0479</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="D158" s="63" t="s">
-        <v>760</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -12647,12 +12590,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16088,7 +16031,7 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">WACC!D14</f>
-        <v>0.04719</v>
+        <v>0.085206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16106,7 +16049,7 @@
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">WACC!D19</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16115,7 +16058,7 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">WACC!D22</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>72</v>
@@ -16150,7 +16093,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">'Valor justo'!E10</f>
-        <v>0.883587455256839</v>
+        <v>0.875829030426722</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>77</v>
@@ -16162,7 +16105,7 @@
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">'Valor justo'!E11</f>
-        <v>23906.8310556065</v>
+        <v>23696.9148208663</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16171,7 +16114,7 @@
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>105265.59403105</v>
+        <v>103229.505319693</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16215,7 +16158,7 @@
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">'Valor justo'!D17</f>
-        <v>569989.379756602</v>
+        <v>516407.475225762</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16224,7 +16167,7 @@
       </c>
       <c r="C34" s="21" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>327159.592579581</v>
+        <v>284907.812990989</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16247,7 +16190,7 @@
       </c>
       <c r="C38" s="17" t="n">
         <f aca="false">'Valor justo'!D21</f>
-        <v>105265.59403105</v>
+        <v>103229.505319693</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16256,7 +16199,7 @@
       </c>
       <c r="C39" s="17" t="n">
         <f aca="false">'Valor justo'!D18</f>
-        <v>327159.592579581</v>
+        <v>284907.812990989</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16265,7 +16208,7 @@
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>432425.186610631</v>
+        <v>388137.318310682</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16288,7 +16231,7 @@
       </c>
       <c r="C44" s="17" t="n">
         <f aca="false">'Valor justo'!D22</f>
-        <v>432425.186610631</v>
+        <v>388137.318310682</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16333,7 +16276,7 @@
       </c>
       <c r="C48" s="21" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>386649.186610631</v>
+        <v>342361.318310682</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16356,7 +16299,7 @@
       </c>
       <c r="C52" s="17" t="n">
         <f aca="false">'Valor justo'!D27</f>
-        <v>386649.186610631</v>
+        <v>342361.318310682</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16374,7 +16317,7 @@
       </c>
       <c r="C54" s="25" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16392,7 +16335,7 @@
       </c>
       <c r="C56" s="11" t="n">
         <f aca="false">'Valor justo'!D31</f>
-        <v>0.403675433288633</v>
+        <v>0.242894562985227</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>106</v>
@@ -19600,24 +19543,24 @@
         <v>268</v>
       </c>
       <c r="D17" s="17" t="n">
-        <f aca="false">C38*Premissas!$D$25</f>
+        <f aca="false">C38*Premissas!$D$24</f>
         <v>3896.4744</v>
       </c>
       <c r="E17" s="17" t="n">
-        <f aca="false">D38*Premissas!$D$25</f>
-        <v>3693.02185404644</v>
+        <f aca="false">D38*Premissas!$D$24</f>
+        <v>3543.0526541656</v>
       </c>
       <c r="F17" s="17" t="n">
-        <f aca="false">E38*Premissas!$D$25</f>
-        <v>3548.33432871972</v>
+        <f aca="false">E38*Premissas!$D$24</f>
+        <v>3245.42202532735</v>
       </c>
       <c r="G17" s="17" t="n">
-        <f aca="false">F38*Premissas!$D$25</f>
-        <v>3488.32384932126</v>
+        <f aca="false">F38*Premissas!$D$24</f>
+        <v>3029.4355659922</v>
       </c>
       <c r="H17" s="17" t="n">
-        <f aca="false">G38*Premissas!$D$25</f>
-        <v>3518.97246691831</v>
+        <f aca="false">G38*Premissas!$D$24</f>
+        <v>2901.01518499671</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>269</v>
@@ -19629,23 +19572,23 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">C42*Premissas!$D$23</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">D42*Premissas!$D$23</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">E42*Premissas!$D$23</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">F42*Premissas!$D$23</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="H18" s="17" t="n">
         <f aca="false">G42*Premissas!$D$23</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>271</v>
@@ -19661,23 +19604,23 @@
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">D17-D18</f>
-        <v>-1897.1176</v>
+        <v>-9459.8243</v>
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">E17-E18</f>
-        <v>-2100.57014595356</v>
+        <v>-9813.2460458344</v>
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">F17-F18</f>
-        <v>-2245.25767128028</v>
+        <v>-10110.8766746726</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">G17-G18</f>
-        <v>-2305.26815067874</v>
+        <v>-10326.8631340078</v>
       </c>
       <c r="H19" s="17" t="n">
         <f aca="false">H17-H18</f>
-        <v>-2274.61953308169</v>
+        <v>-10455.2835150033</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>273</v>
@@ -19693,23 +19636,23 @@
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">D16+D19</f>
-        <v>57068.31046945</v>
+        <v>49505.60376945</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">E16+E19</f>
-        <v>61539.7734467501</v>
+        <v>53827.0975468693</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">F16+F19</f>
-        <v>66377.2608320537</v>
+        <v>58511.6418286614</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">G16+G19</f>
-        <v>71621.0665504898</v>
+        <v>63599.4715671608</v>
       </c>
       <c r="H20" s="17" t="n">
         <f aca="false">H16+H19</f>
-        <v>77292.3261139598</v>
+        <v>69111.6621320382</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>274</v>
@@ -19725,23 +19668,23 @@
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">MAX(0,D20-D13)*Premissas!$D$22</f>
-        <v>19937.025559613</v>
+        <v>17365.705281613</v>
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">MAX(0,E20-E13)*Premissas!$D$22</f>
-        <v>21457.322971895</v>
+        <v>18835.0131659356</v>
       </c>
       <c r="F21" s="17" t="n">
         <f aca="false">MAX(0,F20-F13)*Premissas!$D$22</f>
-        <v>23102.0686828983</v>
+        <v>20427.7582217449</v>
       </c>
       <c r="G21" s="17" t="n">
         <f aca="false">MAX(0,G20-G13)*Premissas!$D$22</f>
-        <v>24884.9626271665</v>
+        <v>22157.6203328347</v>
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">MAX(0,H20-H13)*Premissas!$D$22</f>
-        <v>26813.1908787463</v>
+        <v>24031.765124893</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>276</v>
@@ -19757,23 +19700,23 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D20-D21</f>
-        <v>37131.284909837</v>
+        <v>32139.898487837</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">E20-E21</f>
-        <v>40082.4504748551</v>
+        <v>34992.0843809337</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">F20-F21</f>
-        <v>43275.1921491555</v>
+        <v>38083.8836069165</v>
       </c>
       <c r="G22" s="31" t="n">
         <f aca="false">G20-G21</f>
-        <v>46736.1039233233</v>
+        <v>41441.8512343261</v>
       </c>
       <c r="H22" s="31" t="n">
         <f aca="false">H20-H21</f>
-        <v>50479.1352352134</v>
+        <v>45079.8970071452</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>278</v>
@@ -20026,24 +19969,24 @@
         <v>291</v>
       </c>
       <c r="D34" s="17" t="n">
-        <f aca="false">MAX(0,D22)*Premissas!$D$26</f>
-        <v>25212.1424537793</v>
+        <f aca="false">MAX(0,D22)*Premissas!$D$25</f>
+        <v>21822.9910732413</v>
       </c>
       <c r="E34" s="17" t="n">
-        <f aca="false">MAX(0,E22)*Premissas!$D$26</f>
-        <v>27215.9838724266</v>
+        <f aca="false">MAX(0,E22)*Premissas!$D$25</f>
+        <v>23759.625294654</v>
       </c>
       <c r="F34" s="17" t="n">
-        <f aca="false">MAX(0,F22)*Premissas!$D$26</f>
-        <v>29383.8554692766</v>
+        <f aca="false">MAX(0,F22)*Premissas!$D$25</f>
+        <v>25858.9569690963</v>
       </c>
       <c r="G34" s="17" t="n">
-        <f aca="false">MAX(0,G22)*Premissas!$D$26</f>
-        <v>31733.8145639365</v>
+        <f aca="false">MAX(0,G22)*Premissas!$D$25</f>
+        <v>28139.0169881074</v>
       </c>
       <c r="H34" s="17" t="n">
-        <f aca="false">MAX(0,H22)*Premissas!$D$26</f>
-        <v>34275.3328247099</v>
+        <f aca="false">MAX(0,H22)*Premissas!$D$25</f>
+        <v>30609.2500678516</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>292</v>
@@ -20055,23 +19998,23 @@
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">FCFF!D22-D34</f>
-        <v>-2173.63831146962</v>
+        <v>-3775.87335293162</v>
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">FCFF!E22-E34</f>
-        <v>-1545.8068945163</v>
+        <v>-3179.81441066505</v>
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">FCFF!F22-F34</f>
-        <v>-641.137600410879</v>
+        <v>-2307.54764246958</v>
       </c>
       <c r="G35" s="17" t="n">
         <f aca="false">FCFF!G22-G34</f>
-        <v>327.442495694937</v>
+        <v>-1372.01261747316</v>
       </c>
       <c r="H35" s="17" t="n">
         <f aca="false">FCFF!H22-H34</f>
-        <v>1390.24527876402</v>
+        <v>-342.910192445892</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>294</v>
@@ -20098,23 +20041,23 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">C38+D35</f>
-        <v>39455.3616885304</v>
+        <v>37853.1266470684</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">D38+E35</f>
-        <v>37909.5547940141</v>
+        <v>34673.3122364033</v>
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">E38+F35</f>
-        <v>37268.4171936032</v>
+        <v>32365.7645939337</v>
       </c>
       <c r="G38" s="17" t="n">
         <f aca="false">F38+G35</f>
-        <v>37595.8596892981</v>
+        <v>30993.7519764606</v>
       </c>
       <c r="H38" s="17" t="n">
         <f aca="false">G38+H35</f>
-        <v>38986.1049680622</v>
+        <v>30650.8417840147</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>296</v>
@@ -20194,23 +20137,23 @@
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">D38+D27+D28+D26+D39+D40</f>
-        <v>488361.343507719</v>
+        <v>486759.108466257</v>
       </c>
       <c r="E41" s="31" t="n">
         <f aca="false">E38+E27+E28+E26+E39+E40</f>
-        <v>501819.213259919</v>
+        <v>498582.970702309</v>
       </c>
       <c r="F41" s="31" t="n">
         <f aca="false">F38+F27+F28+F26+F39+F40</f>
-        <v>516301.848149639</v>
+        <v>511399.195549969</v>
       </c>
       <c r="G41" s="31" t="n">
         <f aca="false">G38+G27+G28+G26+G39+G40</f>
-        <v>531894.477824999</v>
+        <v>525292.370112162</v>
       </c>
       <c r="H41" s="31" t="n">
         <f aca="false">H38+H27+H28+H26+H39+H40</f>
-        <v>548686.745370299</v>
+        <v>540351.482186252</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>300</v>
@@ -20290,23 +20233,23 @@
       </c>
       <c r="D44" s="17" t="n">
         <f aca="false">C44+D22-D34</f>
-        <v>200845.142456058</v>
+        <v>199242.907414596</v>
       </c>
       <c r="E44" s="17" t="n">
         <f aca="false">D44+E22-E34</f>
-        <v>213711.609058486</v>
+        <v>210475.366500875</v>
       </c>
       <c r="F44" s="17" t="n">
         <f aca="false">E44+F22-F34</f>
-        <v>227602.945738365</v>
+        <v>222700.293138696</v>
       </c>
       <c r="G44" s="17" t="n">
         <f aca="false">F44+G22-G34</f>
-        <v>242605.235097752</v>
+        <v>236003.127384914</v>
       </c>
       <c r="H44" s="17" t="n">
         <f aca="false">G44+H22-H34</f>
-        <v>258809.037508255</v>
+        <v>250473.774324208</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>304</v>
@@ -20322,23 +20265,23 @@
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">D29+D42+D43+D44</f>
-        <v>488361.343507719</v>
+        <v>486759.108466257</v>
       </c>
       <c r="E45" s="31" t="n">
         <f aca="false">E29+E42+E43+E44</f>
-        <v>501819.213259919</v>
+        <v>498582.970702309</v>
       </c>
       <c r="F45" s="31" t="n">
         <f aca="false">F29+F42+F43+F44</f>
-        <v>516301.848149639</v>
+        <v>511399.195549969</v>
       </c>
       <c r="G45" s="31" t="n">
         <f aca="false">G29+G42+G43+G44</f>
-        <v>531894.477824999</v>
+        <v>525292.370112162</v>
       </c>
       <c r="H45" s="31" t="n">
         <f aca="false">H29+H42+H43+H44</f>
-        <v>548686.745370299</v>
+        <v>540351.482186252</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>306</v>
@@ -20429,23 +20372,23 @@
       </c>
       <c r="D50" s="17" t="n">
         <f aca="false">D42-D38</f>
-        <v>64001.6383114696</v>
+        <v>65603.8733529316</v>
       </c>
       <c r="E50" s="17" t="n">
         <f aca="false">E42-E38</f>
-        <v>65547.4452059859</v>
+        <v>68783.6877635967</v>
       </c>
       <c r="F50" s="17" t="n">
         <f aca="false">F42-F38</f>
-        <v>66188.5828063968</v>
+        <v>71091.2354060663</v>
       </c>
       <c r="G50" s="17" t="n">
         <f aca="false">G42-G38</f>
-        <v>65861.1403107019</v>
+        <v>72463.2480235394</v>
       </c>
       <c r="H50" s="17" t="n">
         <f aca="false">H42-H38</f>
-        <v>64470.8950319378</v>
+        <v>72806.1582159853</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>311</v>
@@ -20461,23 +20404,23 @@
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">D50/D14</f>
-        <v>0.848528127588214</v>
+        <v>0.869770419747543</v>
       </c>
       <c r="E51" s="29" t="n">
         <f aca="false">E50/E14</f>
-        <v>0.809463250969197</v>
+        <v>0.849428491618565</v>
       </c>
       <c r="F51" s="29" t="n">
         <f aca="false">F50/F14</f>
-        <v>0.762207610737904</v>
+        <v>0.81866506859287</v>
       </c>
       <c r="G51" s="29" t="n">
         <f aca="false">G50/G14</f>
-        <v>0.707978788969127</v>
+        <v>0.778948593031553</v>
       </c>
       <c r="H51" s="29" t="n">
         <f aca="false">H50/H14</f>
-        <v>0.647559468993994</v>
+        <v>0.731280636486909</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>312</v>
@@ -20823,23 +20766,23 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">Projeção!D22</f>
-        <v>37131.284909837</v>
+        <v>32139.898487837</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">Projeção!E22</f>
-        <v>40082.4504748551</v>
+        <v>34992.0843809337</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">Projeção!F22</f>
-        <v>43275.1921491555</v>
+        <v>38083.8836069165</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">Projeção!G22</f>
-        <v>46736.1039233233</v>
+        <v>41441.8512343261</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">Projeção!H22</f>
-        <v>50479.1352352134</v>
+        <v>45079.8970071452</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>333</v>
@@ -20991,23 +20934,23 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D16-D17+D18-D19-D20+D21</f>
-        <v>23038.5041423097</v>
+        <v>18047.1177203097</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">E16-E17+E18-E19-E20+E21</f>
-        <v>25670.1769779103</v>
+        <v>20579.8108839889</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">F16-F17+F18-F19-F20+F21</f>
-        <v>28742.7178688657</v>
+        <v>23551.4093266267</v>
       </c>
       <c r="G22" s="31" t="n">
         <f aca="false">G16-G17+G18-G19-G20+G21</f>
-        <v>32061.2570596314</v>
+        <v>26767.0043706343</v>
       </c>
       <c r="H22" s="31" t="n">
         <f aca="false">H16-H17+H18-H19-H20+H21</f>
-        <v>35665.578103474</v>
+        <v>30266.3398754057</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>337</v>
@@ -21029,7 +20972,7 @@
         <v>339</v>
       </c>
       <c r="D25" s="17" t="n">
-        <f aca="false">Premissas!$D$33*H10</f>
+        <f aca="false">Premissas!$D$32*H10</f>
         <v>19992.8602378074</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -21054,7 +20997,7 @@
       </c>
       <c r="D27" s="17" t="n">
         <f aca="false">H16-H17+H18-D25-H20+H21</f>
-        <v>51464.6704385988</v>
+        <v>46065.4322105305</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>344</v>
@@ -21113,7 +21056,7 @@
         <v>347</v>
       </c>
       <c r="D5" s="18" t="n">
-        <f aca="false">Premissas!$D$27</f>
+        <f aca="false">Premissas!$D$26</f>
         <v>0.1291</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -21125,7 +21068,7 @@
         <v>349</v>
       </c>
       <c r="D6" s="30" t="n">
-        <f aca="false">Premissas!$D$28</f>
+        <f aca="false">Premissas!$D$27</f>
         <v>0.7558</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -21137,7 +21080,7 @@
         <v>351</v>
       </c>
       <c r="D7" s="18" t="n">
-        <f aca="false">Premissas!$D$29</f>
+        <f aca="false">Premissas!$D$28</f>
         <v>0.0423</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -21149,7 +21092,7 @@
         <v>353</v>
       </c>
       <c r="D8" s="18" t="n">
-        <f aca="false">Premissas!$D$30</f>
+        <f aca="false">Premissas!$D$29</f>
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -21185,8 +21128,8 @@
         <v>358</v>
       </c>
       <c r="D12" s="18" t="n">
-        <f aca="false">Premissas!$D$24</f>
-        <v>0.0715</v>
+        <f aca="false">Premissas!$D$23</f>
+        <v>0.1291</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>359</v>
@@ -21210,7 +21153,7 @@
       </c>
       <c r="D14" s="32" t="n">
         <f aca="false">D12*(1-D13)</f>
-        <v>0.04719</v>
+        <v>0.085206</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>363</v>
@@ -21233,7 +21176,7 @@
         <v>69</v>
       </c>
       <c r="D17" s="18" t="n">
-        <f aca="false">Premissas!$D$31</f>
+        <f aca="false">Premissas!$D$30</f>
         <v>0.2625</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -21258,7 +21201,7 @@
       </c>
       <c r="D19" s="32" t="n">
         <f aca="false">D9*D18+D14*D17</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>369</v>
@@ -21282,7 +21225,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">Painel!$C$12</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>372</v>
@@ -21329,7 +21272,7 @@
         <v>378</v>
       </c>
       <c r="D27" s="17" t="n">
-        <f aca="false">Premissas!$D$40</f>
+        <f aca="false">Premissas!$D$39</f>
         <v>275454.8362</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -21464,7 +21407,7 @@
         <v>388</v>
       </c>
       <c r="D7" s="33" t="n">
-        <f aca="false">(DATE(2026,12,31)-Premissas!$D$37)/365</f>
+        <f aca="false">(DATE(2026,12,31)-Premissas!$D$36)/365</f>
         <v>0.504109589041096</v>
       </c>
       <c r="E7" s="33" t="n">
@@ -21545,23 +21488,23 @@
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^D9</f>
-        <v>0.969409760890913</v>
+        <v>0.967265990340734</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^E9</f>
-        <v>0.883587455256839</v>
+        <v>0.875829030426722</v>
       </c>
       <c r="F10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^F9</f>
-        <v>0.781122361886414</v>
+        <v>0.767492847801479</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^G9</f>
-        <v>0.690539618471215</v>
+        <v>0.672557372458218</v>
       </c>
       <c r="H10" s="23" t="n">
         <f aca="false">1/(1+WACC!$D$22)^H9</f>
-        <v>0.610461289991479</v>
+        <v>0.589364996095576</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>395</v>
@@ -21573,23 +21516,23 @@
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">D6*D7*D10</f>
-        <v>11870.5439600142</v>
+        <v>11844.2932210772</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">E6*E7*E10</f>
-        <v>23906.8310556065</v>
+        <v>23696.9148208663</v>
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">F6*F7*F10</f>
-        <v>23609.1015124177</v>
+        <v>23197.1550654883</v>
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">G6*G7*G10</f>
-        <v>23190.2083505662</v>
+        <v>22586.3153652864</v>
       </c>
       <c r="H11" s="31" t="n">
         <f aca="false">H6*H7*H10</f>
-        <v>22688.9091524458</v>
+        <v>21904.8268469746</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>397</v>
@@ -21612,7 +21555,7 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">WACC!$D$22</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>400</v>
@@ -21623,7 +21566,7 @@
         <v>401</v>
       </c>
       <c r="D15" s="18" t="n">
-        <f aca="false">Premissas!$D$32</f>
+        <f aca="false">Premissas!$D$31</f>
         <v>0.035</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -21648,7 +21591,7 @@
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">D16*(1+D15)/(D14-D15)</f>
-        <v>569989.379756602</v>
+        <v>516407.475225762</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>405</v>
@@ -21660,7 +21603,7 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D17/(1+D14)^H8</f>
-        <v>327159.592579581</v>
+        <v>284907.812990989</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>407</v>
@@ -21683,7 +21626,7 @@
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">SUM($D$11:$H$11)</f>
-        <v>105265.59403105</v>
+        <v>103229.505319693</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>409</v>
@@ -21695,7 +21638,7 @@
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">D21+D18</f>
-        <v>432425.186610631</v>
+        <v>388137.318310682</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>411</v>
@@ -21742,7 +21685,7 @@
         <v>418</v>
       </c>
       <c r="D26" s="17" t="n">
-        <f aca="false">Premissas!$D$34</f>
+        <f aca="false">Premissas!$D$33</f>
         <v>0</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -21755,7 +21698,7 @@
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">D22-D23-D24+D25-D26</f>
-        <v>386649.186610631</v>
+        <v>342361.318310682</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>421</v>
@@ -21766,7 +21709,7 @@
         <v>422</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">Premissas!$D$38</f>
+        <f aca="false">Premissas!$D$37</f>
         <v>4072.366</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -21779,7 +21722,7 @@
       </c>
       <c r="D29" s="25" t="n">
         <f aca="false">D27/D28</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>424</v>
@@ -21790,7 +21733,7 @@
         <v>26</v>
       </c>
       <c r="D30" s="16" t="n">
-        <f aca="false">Premissas!$D$39</f>
+        <f aca="false">Premissas!$D$38</f>
         <v>67.64</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -21803,7 +21746,7 @@
       </c>
       <c r="D31" s="11" t="n">
         <f aca="false">D29/D30-1</f>
-        <v>0.403675433288633</v>
+        <v>0.242894562985227</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>29</v>
@@ -21815,7 +21758,7 @@
       </c>
       <c r="D32" s="11" t="n">
         <f aca="false">D18/D22</f>
-        <v>0.756569234886324</v>
+        <v>0.734038701125195</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>427</v>
@@ -21827,7 +21770,7 @@
       </c>
       <c r="D33" s="29" t="n">
         <f aca="false">D22/Projeção!D14</f>
-        <v>5.73305533416239</v>
+        <v>5.14589064658759</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>429</v>
@@ -21850,23 +21793,23 @@
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">FCFF!D22</f>
-        <v>23038.5041423097</v>
+        <v>18047.1177203097</v>
       </c>
       <c r="E36" s="31" t="n">
         <f aca="false">FCFF!E22</f>
-        <v>25670.1769779103</v>
+        <v>20579.8108839889</v>
       </c>
       <c r="F36" s="31" t="n">
         <f aca="false">FCFF!F22</f>
-        <v>28742.7178688657</v>
+        <v>23551.4093266267</v>
       </c>
       <c r="G36" s="31" t="n">
         <f aca="false">FCFF!G22</f>
-        <v>32061.2570596314</v>
+        <v>26767.0043706343</v>
       </c>
       <c r="H36" s="31" t="n">
         <f aca="false">FCFF!H22</f>
-        <v>35665.578103474</v>
+        <v>30266.3398754057</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>432</v>
@@ -21906,23 +21849,23 @@
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">D36*D7*D37</f>
-        <v>11184.8800870152</v>
+        <v>8761.62993790941</v>
       </c>
       <c r="E38" s="17" t="n">
         <f aca="false">E36*E7*E37</f>
-        <v>22095.4977754143</v>
+        <v>17713.9863896116</v>
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">F36*F7*F37</f>
-        <v>21308.0755582567</v>
+        <v>17459.5600779558</v>
       </c>
       <c r="G38" s="17" t="n">
         <f aca="false">G36*G7*G37</f>
-        <v>20470.9695059695</v>
+        <v>17090.6127984398</v>
       </c>
       <c r="H38" s="17" t="n">
         <f aca="false">H36*H7*H37</f>
-        <v>19613.2065540443</v>
+        <v>16644.0587024557</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>436</v>
@@ -21946,7 +21889,7 @@
       </c>
       <c r="D40" s="17" t="n">
         <f aca="false">FCFF!D27</f>
-        <v>51464.6704385988</v>
+        <v>46065.4322105305</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>439</v>
@@ -21958,7 +21901,7 @@
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">D40*(1+D15)/(D39-D15)/(1+D39)^H8</f>
-        <v>215628.762488522</v>
+        <v>193006.815285186</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>441</v>
@@ -21970,7 +21913,7 @@
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">SUM($D$38:$H$38)+D41-D24+D25-D26</f>
-        <v>332717.391969222</v>
+        <v>293092.663191558</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>443</v>
@@ -21982,7 +21925,7 @@
       </c>
       <c r="D43" s="16" t="n">
         <f aca="false">D42/D28</f>
-        <v>81.7012498309882</v>
+        <v>71.9711006308269</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>445</v>
@@ -22030,131 +21973,131 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="34" t="n">
         <f aca="false">$D$14+-2*0.01</f>
-        <v>0.11117675075</v>
+        <v>0.12115595075</v>
       </c>
       <c r="D47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+D$46)/($C47-D$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>111.885663287535</v>
+        <v>97.9596452787297</v>
       </c>
       <c r="E47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+E$46)/($C47-E$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>118.310598845127</v>
+        <v>102.92926692267</v>
       </c>
       <c r="F47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+F$46)/($C47-F$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>125.578959134587</v>
+        <v>108.475705559596</v>
       </c>
       <c r="G47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+G$46)/($C47-G$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>133.868489990682</v>
+        <v>114.705573887834</v>
       </c>
       <c r="H47" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C47)^$D$9:$H$9)+$D$16*(1+H$46)/($C47-H$46)/(1+$C47)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>143.410655761932</v>
+        <v>121.753483126453</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="34" t="n">
         <f aca="false">$D$14+-1*0.01</f>
-        <v>0.12117675075</v>
+        <v>0.13115595075</v>
       </c>
       <c r="D48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+D$46)/($C48-D$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>97.933713472542</v>
+        <v>86.6963661597229</v>
       </c>
       <c r="E48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+E$46)/($C48-E$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>102.900803963437</v>
+        <v>90.6285633105005</v>
       </c>
       <c r="F48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+F$46)/($C48-F$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>108.444278507765</v>
+        <v>94.9697000141717</v>
       </c>
       <c r="G48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+G$46)/($C48-G$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>114.670642486951</v>
+        <v>99.7870685675417</v>
       </c>
       <c r="H48" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+H$46)/($C48-H$46)/(1+$C48)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>121.714363982424</v>
+        <v>105.163582311863</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="34" t="n">
         <f aca="false">$D$14+0*0.01</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="D49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+D$46)/($C49-D$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>86.6752149546068</v>
+        <v>77.4285830281698</v>
       </c>
       <c r="E49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+E$46)/($C49-E$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>90.6055803059333</v>
+        <v>80.5996277913376</v>
       </c>
       <c r="F49" s="25" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+F$46)/($C49-F$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="G49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+G$46)/($C49-G$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>99.7595240214417</v>
+        <v>87.882159695899</v>
       </c>
       <c r="H49" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+H$46)/($C49-H$46)/(1+$C49)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>105.133167571605</v>
+        <v>92.0914507039167</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="34" t="n">
         <f aca="false">$D$14+1*0.01</f>
-        <v>0.14117675075</v>
+        <v>0.15115595075</v>
       </c>
       <c r="D50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+D$46)/($C50-D$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>77.4110248998399</v>
+        <v>69.6786574917499</v>
       </c>
       <c r="E50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+E$46)/($C50-E$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>80.5807063123081</v>
+        <v>72.2767009953681</v>
       </c>
       <c r="F50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+F$46)/($C50-F$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>84.0489164883783</v>
+        <v>75.0984130658433</v>
       </c>
       <c r="G50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+G$46)/($C50-G$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>87.8599139303333</v>
+        <v>78.1739767791174</v>
       </c>
       <c r="H50" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+H$46)/($C50-H$46)/(1+$C50)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>92.067160716567</v>
+        <v>81.5392617648727</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C51" s="34" t="n">
         <f aca="false">$D$14+2*0.01</f>
-        <v>0.15117675075</v>
+        <v>0.16115595075</v>
       </c>
       <c r="D51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+D$46)/($C51-D$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>69.6638664549153</v>
+        <v>63.1094664363626</v>
       </c>
       <c r="E51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+E$46)/($C51-E$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>72.2608713618896</v>
+        <v>65.2667711026161</v>
       </c>
       <c r="F51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+F$46)/($C51-F$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>75.0814153926739</v>
+        <v>67.5950787737559</v>
       </c>
       <c r="G51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+G$46)/($C51-G$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>78.1556585117799</v>
+        <v>70.1155608826122</v>
       </c>
       <c r="H51" s="16" t="n">
         <f aca="false">(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+H$46)/($C51-H$46)/(1+$C51)^$H$8-$D$23-$D$24+$D$25-$D$26)/$D$28</f>
-        <v>81.5194417700774</v>
+        <v>72.8530342082407</v>
       </c>
     </row>
   </sheetData>
@@ -22645,7 +22588,7 @@
       </c>
       <c r="C20" s="36" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>481</v>
@@ -22792,19 +22735,19 @@
       </c>
       <c r="E7" s="17" t="n">
         <f aca="false">Projeção!E17</f>
-        <v>3693.02185404644</v>
+        <v>3543.0526541656</v>
       </c>
       <c r="F7" s="17" t="n">
         <f aca="false">Projeção!F17</f>
-        <v>3548.33432871972</v>
+        <v>3245.42202532735</v>
       </c>
       <c r="G7" s="17" t="n">
         <f aca="false">Projeção!G17</f>
-        <v>3488.32384932126</v>
+        <v>3029.4355659922</v>
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">Projeção!H17</f>
-        <v>3518.97246691831</v>
+        <v>2901.01518499671</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>492</v>
@@ -22848,19 +22791,19 @@
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">E6+E7+E8</f>
-        <v>86239.4529983928</v>
+        <v>86089.483798512</v>
       </c>
       <c r="F9" s="31" t="n">
         <f aca="false">F6+F7+F8</f>
-        <v>91956.3321050981</v>
+        <v>91653.4198017057</v>
       </c>
       <c r="G9" s="31" t="n">
         <f aca="false">G6+G7+G8</f>
-        <v>98085.3203312369</v>
+        <v>97626.4320479079</v>
       </c>
       <c r="H9" s="31" t="n">
         <f aca="false">H6+H7+H8</f>
-        <v>104648.778351767</v>
+        <v>104030.821069846</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>496</v>
@@ -22883,23 +22826,23 @@
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Projeção!D21</f>
-        <v>19937.025559613</v>
+        <v>17365.705281613</v>
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">Projeção!E21</f>
-        <v>21457.322971895</v>
+        <v>18835.0131659356</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">Projeção!F21</f>
-        <v>23102.0686828983</v>
+        <v>20427.7582217449</v>
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">Projeção!G21</f>
-        <v>24884.9626271665</v>
+        <v>22157.6203328347</v>
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">Projeção!H21</f>
-        <v>26813.1908787463</v>
+        <v>24031.765124893</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>498</v>
@@ -22967,23 +22910,23 @@
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Projeção!D18</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">Projeção!E18</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="F14" s="17" t="n">
         <f aca="false">Projeção!F18</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">Projeção!G18</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">Projeção!H18</f>
-        <v>5793.592</v>
+        <v>13356.2987</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>503</v>
@@ -23023,23 +22966,23 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">Projeção!D34</f>
-        <v>25212.1424537793</v>
+        <v>21822.9910732413</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">Projeção!E34</f>
-        <v>27215.9838724266</v>
+        <v>23759.625294654</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">Projeção!F34</f>
-        <v>29383.8554692766</v>
+        <v>25858.9569690963</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">Projeção!G34</f>
-        <v>31733.8145639365</v>
+        <v>28139.0169881074</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">Projeção!H34</f>
-        <v>34275.3328247099</v>
+        <v>30609.2500678516</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>507</v>
@@ -23051,23 +22994,23 @@
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">SUM(D11:D16)</f>
-        <v>83066.7676809196</v>
+        <v>84669.0027223816</v>
       </c>
       <c r="E17" s="31" t="n">
         <f aca="false">SUM(E11:E16)</f>
-        <v>87785.2598929091</v>
+        <v>89269.298209177</v>
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">SUM(F11:F16)</f>
-        <v>92597.4697055089</v>
+        <v>93960.9674441753</v>
       </c>
       <c r="G17" s="31" t="n">
         <f aca="false">SUM(G11:G16)</f>
-        <v>97757.877835542</v>
+        <v>98998.444665381</v>
       </c>
       <c r="H17" s="31" t="n">
         <f aca="false">SUM(H11:H16)</f>
-        <v>103258.533073003</v>
+        <v>104373.731262291</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>509</v>
@@ -23090,23 +23033,23 @@
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">D9-D17</f>
-        <v>-2173.63831146962</v>
+        <v>-3775.87335293161</v>
       </c>
       <c r="E19" s="31" t="n">
         <f aca="false">E9-E17</f>
-        <v>-1545.80689451631</v>
+        <v>-3179.81441066504</v>
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">F9-F17</f>
-        <v>-641.137600410861</v>
+        <v>-2307.5476424696</v>
       </c>
       <c r="G19" s="31" t="n">
         <f aca="false">G9-G17</f>
-        <v>327.442495694937</v>
+        <v>-1372.01261747316</v>
       </c>
       <c r="H19" s="31" t="n">
         <f aca="false">H9-H17</f>
-        <v>1390.24527876402</v>
+        <v>-342.91019244591</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>512</v>
@@ -23118,23 +23061,23 @@
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">Projeção!D38</f>
-        <v>39455.3616885304</v>
+        <v>37853.1266470684</v>
       </c>
       <c r="E20" s="17" t="n">
         <f aca="false">Projeção!E38</f>
-        <v>37909.5547940141</v>
+        <v>34673.3122364033</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">Projeção!F38</f>
-        <v>37268.4171936032</v>
+        <v>32365.7645939337</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">Projeção!G38</f>
-        <v>37595.8596892981</v>
+        <v>30993.7519764606</v>
       </c>
       <c r="H20" s="17" t="n">
         <f aca="false">Projeção!H38</f>
-        <v>38986.1049680622</v>
+        <v>30650.8417840147</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>514</v>
@@ -23150,11 +23093,11 @@
       </c>
       <c r="E21" s="17" t="n">
         <f aca="false">ROUND(E19-Projeção!E35,3)</f>
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17" t="n">
         <f aca="false">ROUND(F19-Projeção!F35,3)</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G21" s="17" t="n">
         <f aca="false">ROUND(G19-Projeção!G35,3)</f>
@@ -23162,7 +23105,7 @@
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">ROUND(H19-Projeção!H35,3)</f>
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>516</v>
@@ -23189,15 +23132,15 @@
       </c>
       <c r="D25" s="41" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>56.9203936118611</v>
+        <v>51.0489960521451</v>
       </c>
       <c r="E25" s="41" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>94.9446063076432</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="F25" s="41" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>159.343024237654</v>
+        <v>138.611356353207</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23206,15 +23149,15 @@
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>277576.67565156</v>
+        <v>253666.19585689</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>432425.186610632</v>
+        <v>388137.318310682</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>694679.114242599</v>
+        <v>610252.174826684</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23223,15 +23166,15 @@
       </c>
       <c r="D27" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>231800.67565156</v>
+        <v>207890.19585689</v>
       </c>
       <c r="E27" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>386649.186610632</v>
+        <v>342361.318310682</v>
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>648903.114242599</v>
+        <v>564476.174826684</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23240,15 +23183,15 @@
       </c>
       <c r="D28" s="11" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.14677675075</v>
+        <v>0.15675595075</v>
       </c>
       <c r="E28" s="11" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="F28" s="11" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.11557675075</v>
+        <v>0.12555595075</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23308,15 +23251,15 @@
       </c>
       <c r="D32" s="17" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>40797.5333671632</v>
+        <v>32462.2701831158</v>
       </c>
       <c r="E32" s="17" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>38986.1049680622</v>
+        <v>30650.8417840147</v>
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>41622.8194530891</v>
+        <v>33287.5562690417</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23325,15 +23268,15 @@
       </c>
       <c r="D33" s="29" t="n">
         <f aca="false">INDEX(D$1:D$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.824772669815776</v>
+        <v>0.934487891463087</v>
       </c>
       <c r="E33" s="29" t="n">
         <f aca="false">INDEX(E$1:E$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.647559468993994</v>
+        <v>0.731280636486909</v>
       </c>
       <c r="F33" s="29" t="n">
         <f aca="false">INDEX(F$1:F$72,ROW()+12*Painel!$Y$5)</f>
-        <v>0.479329634758266</v>
+        <v>0.543943390811722</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23356,13 +23299,13 @@
         <v>24</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>56.9203936118611</v>
+        <v>51.0489960521451</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>94.9446063076432</v>
+        <v>84.0693882403208</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>159.343024237654</v>
+        <v>138.611356353207</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23370,13 +23313,13 @@
         <v>30</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>277576.67565156</v>
+        <v>253666.19585689</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>432425.186610632</v>
+        <v>388137.318310682</v>
       </c>
       <c r="F38" s="17" t="n">
-        <v>694679.114242599</v>
+        <v>610252.174826684</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23384,13 +23327,13 @@
         <v>32</v>
       </c>
       <c r="D39" s="17" t="n">
-        <v>231800.67565156</v>
+        <v>207890.19585689</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>386649.186610632</v>
+        <v>342361.318310682</v>
       </c>
       <c r="F39" s="17" t="n">
-        <v>648903.114242599</v>
+        <v>564476.174826684</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23398,13 +23341,13 @@
         <v>399</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.14677675075</v>
+        <v>0.15675595075</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.13117675075</v>
+        <v>0.14115595075</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.11557675075</v>
+        <v>0.12555595075</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23454,13 +23397,13 @@
         <v>520</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>40797.5333671632</v>
+        <v>32462.2701831158</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>38986.1049680622</v>
+        <v>30650.8417840147</v>
       </c>
       <c r="F44" s="17" t="n">
-        <v>41622.8194530891</v>
+        <v>33287.5562690417</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23468,13 +23411,13 @@
         <v>521</v>
       </c>
       <c r="D45" s="29" t="n">
-        <v>0.824772669815776</v>
+        <v>0.934487891463087</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>0.647559468993994</v>
+        <v>0.731280636486909</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>0.479329634758266</v>
+        <v>0.543943390811722</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23595,13 +23538,13 @@
         <v>520</v>
       </c>
       <c r="D56" s="17" t="n">
-        <v>11626.8757892491</v>
+        <v>-3687.46361135201</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>11366.9708296553</v>
+        <v>-1569.66014190046</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>13099.8580403209</v>
+        <v>3105.15012697354</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23609,13 +23552,13 @@
         <v>521</v>
       </c>
       <c r="D57" s="29" t="n">
-        <v>4.85959661759654</v>
+        <v>6.66167188649241</v>
       </c>
       <c r="E57" s="29" t="n">
-        <v>3.96722679187521</v>
+        <v>5.20220134324432</v>
       </c>
       <c r="F57" s="29" t="n">
-        <v>2.76062163176999</v>
+        <v>3.45344830762287</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23638,13 +23581,13 @@
         <v>24</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>11.9396986702007</v>
+        <v>11.4949241466429</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>22.3229527459937</v>
+        <v>21.3835729098938</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>42.8784481671766</v>
+        <v>40.8409931438173</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23652,13 +23595,13 @@
         <v>30</v>
       </c>
       <c r="D62" s="17" t="n">
-        <v>28046.7677991838</v>
+        <v>27173.5950831609</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>48430.9707656516</v>
+        <v>46586.798495389</v>
       </c>
       <c r="F62" s="17" t="n">
-        <v>88785.1205999066</v>
+        <v>84785.2284246752</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23666,13 +23609,13 @@
         <v>32</v>
       </c>
       <c r="D63" s="17" t="n">
-        <v>23439.7847991838</v>
+        <v>22566.6120831609</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>43823.9877656516</v>
+        <v>41979.815495389</v>
       </c>
       <c r="F63" s="17" t="n">
-        <v>84178.1375999066</v>
+        <v>80178.2454246751</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23680,13 +23623,13 @@
         <v>399</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>0.156832395041</v>
+        <v>0.160612848641</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.141232395041</v>
+        <v>0.145012848641</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>0.125632395041</v>
+        <v>0.129412848641</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23736,13 +23679,13 @@
         <v>520</v>
       </c>
       <c r="D68" s="17" t="n">
-        <v>12250.190935772</v>
+        <v>11133.5419715542</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>13253.6069770103</v>
+        <v>12136.9580127926</v>
       </c>
       <c r="F68" s="17" t="n">
-        <v>17553.2334953957</v>
+        <v>16436.5845311779</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23750,13 +23693,13 @@
         <v>521</v>
       </c>
       <c r="D69" s="29" t="n">
-        <v>0.172227722212721</v>
+        <v>0.271773210330905</v>
       </c>
       <c r="E69" s="29" t="n">
-        <v>0.0583983382894964</v>
+        <v>0.128627042958816</v>
       </c>
       <c r="F69" s="29" t="n">
-        <v>-0.152639192091905</v>
+        <v>-0.102078460937666</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23765,7 +23708,7 @@
       </c>
       <c r="D73" s="25" t="n">
         <f aca="false">'Valor justo'!D29</f>
-        <v>94.9446063076431</v>
+        <v>84.0693882403208</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/saida/valuation_vale_csn_gerdau.xlsx
+++ b/saida/valuation_vale_csn_gerdau.xlsx
@@ -2233,13 +2233,13 @@
     <t xml:space="preserve">De onde veio</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.8% ao ano).</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,8% ao ano).</t>
   </si>
   <si>
     <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Daí até 2030 em linha reta. Faixa: margem EBITDA de 2021 a 2025, sem perdas por recuperabilidade. Pessimista é o segundo pior ano, moderado a mediana e otimista o segundo melhor.</t>
   </si>
   <si>
-    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12.2% a 15.3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
+    <t xml:space="preserve">Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12,2% a 15,3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
   </si>
   <si>
     <t xml:space="preserve">Vendas, administrativas e outras, sem perdas por recuperabilidade. Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
@@ -2260,7 +2260,7 @@
     <t xml:space="preserve">Alíquota nominal: IRPJ 25% + CSLL 9%.</t>
   </si>
   <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 17.8%.</t>
+    <t xml:space="preserve">A taxa do Tesouro prefixado de dez anos, a mesma para as três empresas. Custo implícito mediano 2023-2025: 17,8%.</t>
   </si>
   <si>
     <t xml:space="preserve">Mediana 2023-2025 da receita financeira sobre o caixa médio.</t>
@@ -2272,7 +2272,7 @@
     <t xml:space="preserve">Tesouro prefixado de dez anos (em reais, nominal).</t>
   </si>
   <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.64.</t>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,64.</t>
   </si>
   <si>
     <t xml:space="preserve">Damodaran, mercado maduro. O risco-país já está no juro em reais.</t>
@@ -2311,22 +2311,22 @@
     <t xml:space="preserve">Pregão do preço acima.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10.0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 14.2%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1.48.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.1% ao ano).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 19.3%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.71.</t>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (10,0% ao ano), limitado a 4% acima da inflação porque parte veio de aquisições.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A taxa do Tesouro prefixado de dez anos, a mesma para as três empresas. Custo implícito mediano 2023-2025: 14,2%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 1,48.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6,1% ao ano).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A taxa do Tesouro prefixado de dez anos, a mesma para as três empresas. Custo implícito mediano 2023-2025: 19,3%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0,71.</t>
   </si>
   <si>
     <t xml:space="preserve">Dados da CVM</t>
@@ -2986,11 +2986,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="382606"/>
-        <c:axId val="86157532"/>
+        <c:axId val="65242280"/>
+        <c:axId val="71378906"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="382606"/>
+        <c:axId val="65242280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3022,7 +3022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86157532"/>
+        <c:crossAx val="71378906"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3030,7 +3030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86157532"/>
+        <c:axId val="71378906"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3072,7 +3072,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="382606"/>
+        <c:crossAx val="65242280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4124,11 +4124,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="58037023"/>
-        <c:axId val="28988576"/>
+        <c:axId val="80750784"/>
+        <c:axId val="97798197"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58037023"/>
+        <c:axId val="80750784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4160,7 +4160,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28988576"/>
+        <c:crossAx val="97798197"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4168,7 +4168,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28988576"/>
+        <c:axId val="97798197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,7 +4210,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58037023"/>
+        <c:crossAx val="80750784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4790,11 +4790,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="94622550"/>
-        <c:axId val="19950160"/>
+        <c:axId val="3846684"/>
+        <c:axId val="90065978"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="94622550"/>
+        <c:axId val="3846684"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4836,12 +4836,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19950160"/>
+        <c:crossAx val="90065978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="19950160"/>
+        <c:axId val="90065978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4883,7 +4883,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94622550"/>
+        <c:crossAx val="3846684"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>

--- a/saida/valuation_vale_csn_gerdau.xlsx
+++ b/saida/valuation_vale_csn_gerdau.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Escolha a empresa e o cenário nas células amarelas. Todas as abas recalculam.</t>
   </si>
   <si>
-    <t xml:space="preserve">Estudo acadêmico e de portfólio, com dados públicos da CVM e da B3. Não é recomendação de compra ou venda. As premissas são uma proposta por regra, ainda não revisada.</t>
+    <t xml:space="preserve">Isto não é recomendação de investimento. É uma análise feita com os dados que as próprias empresas divulgam e com simulações que juntam dados reais e dados projetados.</t>
   </si>
   <si>
     <t xml:space="preserve">Listas (não apagar)</t>
@@ -2986,11 +2986,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="65242280"/>
-        <c:axId val="71378906"/>
+        <c:axId val="56982360"/>
+        <c:axId val="45477913"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65242280"/>
+        <c:axId val="56982360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3022,7 +3022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71378906"/>
+        <c:crossAx val="45477913"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3030,7 +3030,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71378906"/>
+        <c:axId val="45477913"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3072,7 +3072,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65242280"/>
+        <c:crossAx val="56982360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4124,11 +4124,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="80750784"/>
-        <c:axId val="97798197"/>
+        <c:axId val="2944039"/>
+        <c:axId val="25292030"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="80750784"/>
+        <c:axId val="2944039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4160,7 +4160,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97798197"/>
+        <c:crossAx val="25292030"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4168,7 +4168,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97798197"/>
+        <c:axId val="25292030"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4210,7 +4210,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80750784"/>
+        <c:crossAx val="2944039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4790,11 +4790,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="3846684"/>
-        <c:axId val="90065978"/>
+        <c:axId val="94474264"/>
+        <c:axId val="92860748"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="3846684"/>
+        <c:axId val="94474264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4836,12 +4836,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90065978"/>
+        <c:crossAx val="92860748"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90065978"/>
+        <c:axId val="92860748"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4883,7 +4883,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3846684"/>
+        <c:crossAx val="94474264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>

--- a/saida/valuation_vale_csn_gerdau.xlsx
+++ b/saida/valuation_vale_csn_gerdau.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Painel" sheetId="1" state="visible" r:id="rId3"/>
@@ -19,8 +19,9 @@
     <sheet name="Cenários" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Correlação" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Glossário" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Premissas" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Dados" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Fontes" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Premissas" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Dados" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="890">
   <si>
     <t xml:space="preserve">Valuation de Vale, CSN, Gerdau e Usiminas</t>
   </si>
@@ -2195,6 +2196,321 @@
   </si>
   <si>
     <t xml:space="preserve">Correlação elevada ao quadrado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontes: onde conferir cada dado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum número desta planilha foi digitado à mão. Clique no link para abrir a fonte. Os balanços são os que cada empresa entregou à CVM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endereço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço trimestral (ITR) de 30/06/2026, como a Vale entregou à CVM em 31/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=159978&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço anual (DFP) de 31/12/2025, como a Vale entregou à CVM em 12/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155313&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os documentos da Vale na CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=4170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações com investidores da Vale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.vale.com/pt/investidores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço trimestral (ITR) de 30/06/2026, como a CSN entregou à CVM em 12/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160568&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço anual (DFP) de 31/12/2025, como a CSN entregou à CVM em 11/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155288&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os documentos da CSN na CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=4030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações com investidores da CSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ri.csn.com.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço trimestral (ITR) de 30/06/2026, como a Gerdau entregou à CVM em 04/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160130&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço anual (DFP) de 31/12/2025, como a Gerdau entregou à CVM em 23/02/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=154830&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os documentos da Gerdau na CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=3980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações com investidores da Gerdau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ri.gerdau.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço trimestral (ITR) de 30/06/2026, como a Usiminas entregou à CVM em 30/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=159792&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço anual (DFP) de 31/12/2025, como a Usiminas entregou à CVM em 13/02/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=154757&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os documentos da Usiminas na CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=14320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações com investidores da Usiminas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ri.usiminas.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço trimestral (ITR) de 30/06/2026, como a CSN Mineração entregou à CVM em 12/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160566&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço anual (DFP) de 31/12/2025, como a CSN Mineração entregou à CVM em 12/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155318&amp;CodigoTipoInstituicao=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os documentos da CSN Mineração na CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=25585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações com investidores da CSN Mineração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ri.csnmineracao.com.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanços de todas as companhias abertas, anuais (DFP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CVM, Portal de Dados Abertos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dados.cvm.gov.br/dataset/cia_aberta-doc-dfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanços de todas as companhias abertas, trimestrais (ITR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dados.cvm.gov.br/dataset/cia_aberta-doc-itr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotações diárias de fechamento (arquivo COTAHIST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3, Séries Históricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.b3.com.br/pt_br/market-data-e-indices/servicos-de-dados/market-data/historico/mercado-a-vista/series-historicas/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juro do Tesouro prefixado e do Tesouro IPCA+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesouro Direto, preços e taxas (Tesouro Transparente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tesourotransparente.gov.br/ckan/dataset/taxas-dos-titulos-ofertados-pelo-tesouro-direto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflação esperada (IPCA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Central, Boletim Focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bcb.gov.br/publicacoes/focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aswath Damodaran (NYU), Country Default Spreads and Risk Premiums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minério de ferro 62% Fe, média mensal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Mundial, Commodity Price Data (Pink Sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.worldbank.org/en/research/commodity-markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dólar (PTAX de venda), média mensal, série 3698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Central, Sistema Gerenciador de Séries Temporais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www3.bcb.gov.br/sgspub/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonificação da Gerdau de 5% em ações, de março de 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerdau, aviso aos acionistas de 28/02/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.latibex.com/docs/Documentos/LED/2023/03/02/BRACN_20230301_125502_B01_GGBR3_001_20230322_001_DOC001.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onde achar cada número dentro do documento da CVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em qual demonstração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código da conta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstração do Resultado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perdas por recuperabilidade (impairment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstração do Valor Adicionado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caixa e aplicações financeiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço, Ativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01.01 e 1.01.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dívida (empréstimos e financiamentos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço, Passivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01.04 e 2.02.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caixa das operações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstração do Fluxo de Caixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento (capex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linhas de 6.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividendos pagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linhas de 6.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vale: provisões de Brumadinho e de Mariana (aviso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01.06.02 e 2.02.04.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSN: adiantamentos de clientes, 'passivos de contratos' (aviso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01.05.02 e 2.02.02.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usiminas: perda por recuperabilidade de 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajustes do lucro, em 6.01.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use as demonstrações consolidadas. No documento os valores estão em milhares de reais; aqui, em milhões.</t>
   </si>
   <si>
     <t xml:space="preserve">O primeiro bloco mostra a empresa escolhida no Painel e é o que o modelo lê. Para mudar uma premissa, edite as células azuis no bloco da empresa, mais abaixo.</t>
@@ -2409,7 +2725,7 @@
     <numFmt numFmtId="176" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="177" formatCode="@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2505,6 +2821,14 @@
       <family val="2"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FF1F3864"/>
@@ -2579,7 +2903,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2772,6 +3096,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2869,7 +3197,7 @@
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0563C1"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -3040,11 +3368,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97584856"/>
-        <c:axId val="12894842"/>
+        <c:axId val="24245613"/>
+        <c:axId val="56008615"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97584856"/>
+        <c:axId val="24245613"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3076,7 +3404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12894842"/>
+        <c:crossAx val="56008615"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3084,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12894842"/>
+        <c:axId val="56008615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3126,7 +3454,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97584856"/>
+        <c:crossAx val="24245613"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4178,11 +4506,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="70291635"/>
-        <c:axId val="86478882"/>
+        <c:axId val="71436440"/>
+        <c:axId val="1566079"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70291635"/>
+        <c:axId val="71436440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4214,7 +4542,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86478882"/>
+        <c:crossAx val="1566079"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4222,7 +4550,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86478882"/>
+        <c:axId val="1566079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4264,7 +4592,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70291635"/>
+        <c:crossAx val="71436440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4844,11 +5172,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="48340785"/>
-        <c:axId val="73860544"/>
+        <c:axId val="88362154"/>
+        <c:axId val="9200531"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="48340785"/>
+        <c:axId val="88362154"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4890,12 +5218,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73860544"/>
+        <c:crossAx val="9200531"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="73860544"/>
+        <c:axId val="9200531"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4937,7 +5265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48340785"/>
+        <c:crossAx val="88362154"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11106,2629 +11434,584 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L197"/>
+  <dimension ref="B1:D55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="110"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L4" s="4" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="47" t="str">
-        <f aca="false">"EM USO: "&amp;INDEX($L$5:$L$8,Painel!$Y$5)</f>
-        <v>EM USO: Vale (VALE3)</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>5</v>
+      <c r="B4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="13" t="s">
+        <v>765</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>766</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>723</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="8"/>
-      <c r="L6" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="C7" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0209</v>
-      </c>
-      <c r="D7" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0378</v>
-      </c>
-      <c r="F7" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0683</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="48" t="n">
-        <f aca="false">INDEX(C$1:C$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.3459</v>
-      </c>
-      <c r="D8" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.3484</v>
-      </c>
-      <c r="E8" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.3936</v>
-      </c>
-      <c r="F8" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.4542</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D9" s="32" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0156</v>
-      </c>
-      <c r="E9" s="32" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="32" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-0.0156</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D12" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.083</v>
-      </c>
-      <c r="E12" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0815</v>
-      </c>
-      <c r="F12" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.08</v>
-      </c>
-      <c r="G12" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0785</v>
-      </c>
-      <c r="H12" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.077</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D13" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-1570</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-1570</v>
-      </c>
-      <c r="F13" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-1570</v>
-      </c>
-      <c r="G13" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-1570</v>
-      </c>
-      <c r="H13" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>-1570</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D14" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.146</v>
-      </c>
-      <c r="E14" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1449</v>
-      </c>
-      <c r="F14" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1438</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1427</v>
-      </c>
-      <c r="H14" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1415</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D15" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0569</v>
-      </c>
-      <c r="E15" s="48" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0569</v>
-      </c>
-      <c r="F15" s="48" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0569</v>
-      </c>
-      <c r="G15" s="48" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0569</v>
-      </c>
-      <c r="H15" s="48" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0569</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>21.598</v>
-      </c>
-      <c r="E16" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>21.598</v>
-      </c>
-      <c r="F16" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>21.598</v>
-      </c>
-      <c r="G16" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>21.598</v>
-      </c>
-      <c r="H16" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>21.598</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="D17" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>98.067</v>
-      </c>
-      <c r="E17" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>98.067</v>
-      </c>
-      <c r="F17" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>98.067</v>
-      </c>
-      <c r="G17" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>98.067</v>
-      </c>
-      <c r="H17" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>98.067</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" s="49" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>91.9277</v>
-      </c>
-      <c r="E18" s="49" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>91.9277</v>
-      </c>
-      <c r="F18" s="49" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>91.9277</v>
-      </c>
-      <c r="G18" s="49" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>91.9277</v>
-      </c>
-      <c r="H18" s="49" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>91.9277</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="31" t="n">
-        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="31" t="n">
-        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="31" t="n">
-        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="31" t="n">
-        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="D22" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D23" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1291</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="D24" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0936</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="D25" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.679</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D26" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.1291</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D27" s="50" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.7558</v>
+        <v>767</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D28" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.0423</v>
+        <v>770</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D29" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
+        <v>772</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>773</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="D30" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.2625</v>
+        <v>775</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="D31" s="48" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0.035</v>
+        <v>778</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="D31" s="47" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D32" s="51" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>1</v>
+        <v>356</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>781</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="D33" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>0</v>
+        <v>783</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="D33" s="47" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D34" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>20038</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8"/>
+        <v>786</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="D34" s="47" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="s">
+        <v>789</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>790</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>791</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D37" s="52" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>46203</v>
+      <c r="B37" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="D38" s="53" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>4072.366</v>
+      <c r="B38" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="D39" s="41" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>67.64</v>
+        <v>124</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="D40" s="31" t="n">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>275454.8362</v>
+        <v>128</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D41" s="54" t="str">
-        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
-        <v>2026-10-08</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="47" t="s">
-        <v>5</v>
+        <v>799</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="8" t="s">
-        <v>744</v>
+      <c r="B45" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="C46" s="12" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>0.0683</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>745</v>
+        <v>808</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <v>0.3459</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>0.3484</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>0.3936</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>0.4542</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>746</v>
+        <v>308</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D48" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E48" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>747</v>
+        <v>812</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>813</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>813</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>744</v>
+      <c r="B50" s="0" t="s">
+        <v>817</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>813</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="E51" s="12" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>0.0785</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>748</v>
+        <v>819</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="E52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="F52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="G52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="H52" s="56" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>749</v>
+        <v>821</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="E53" s="12" t="n">
-        <v>0.1449</v>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>0.1438</v>
-      </c>
-      <c r="G53" s="12" t="n">
-        <v>0.1427</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>749</v>
+        <v>823</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>813</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="D55" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="E55" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="F55" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="G55" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="H55" s="57" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="D56" s="57" t="n">
-        <v>98.067</v>
-      </c>
-      <c r="E56" s="57" t="n">
-        <v>98.067</v>
-      </c>
-      <c r="F56" s="57" t="n">
-        <v>98.067</v>
-      </c>
-      <c r="G56" s="57" t="n">
-        <v>98.067</v>
-      </c>
-      <c r="H56" s="57" t="n">
-        <v>98.067</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="D57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="E57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="F57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="G57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="H57" s="57" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>0.0936</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="D64" s="12" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D66" s="58" t="n">
-        <v>0.7558</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="D69" s="12" t="n">
-        <v>0.2625</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="D70" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D71" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="D72" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D73" s="56" t="n">
-        <v>20038</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D76" s="60" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="D77" s="61" t="n">
-        <v>4072.366</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="D78" s="62" t="n">
-        <v>67.64</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="D79" s="56" t="n">
-        <v>275454.8362</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D80" s="63" t="s">
-        <v>770</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="C85" s="12" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>0.0778</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" s="12" t="n">
-        <v>0.1713</v>
-      </c>
-      <c r="D86" s="12" t="n">
-        <v>0.1884</v>
-      </c>
-      <c r="E86" s="12" t="n">
-        <v>0.2002</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D87" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E87" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D90" s="12" t="n">
-        <v>0.2146</v>
-      </c>
-      <c r="E90" s="12" t="n">
-        <v>0.2001</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>0.1713</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>0.1569</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="E91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="F91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="G91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="H91" s="56" t="n">
-        <v>351.131</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>0.1326</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>0.1237</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>0.1148</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>0.1059</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="D94" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="E94" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="F94" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="G94" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="H94" s="57" t="n">
-        <v>19.5303</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="D95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="E95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="F95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="G95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="H95" s="57" t="n">
-        <v>135.0709</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="D96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="E96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="F96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="G96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="H96" s="57" t="n">
-        <v>92.5353</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="D102" s="12" t="n">
-        <v>0.0772</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D104" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D105" s="58" t="n">
-        <v>1.483</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>0.8635</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="D109" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D110" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="D111" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D112" s="56" t="n">
-        <v>13101.338</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D115" s="60" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="D116" s="61" t="n">
-        <v>1326.0939</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="D117" s="62" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="D118" s="56" t="n">
-        <v>8433.9575</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D119" s="63" t="s">
-        <v>770</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="C123" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>-0.0045</v>
-      </c>
-      <c r="D124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C125" s="12" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="D125" s="12" t="n">
-        <v>0.1613</v>
-      </c>
-      <c r="E125" s="12" t="n">
-        <v>0.1971</v>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>0.2506</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D126" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E126" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I128" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D129" s="12" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="E129" s="12" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <v>0.0279</v>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>0.0261</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="E130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="F130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="G130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="H130" s="56" t="n">
-        <v>563.158</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D131" s="12" t="n">
-        <v>0.0804</v>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v>0.0796</v>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>0.0789</v>
-      </c>
-      <c r="G131" s="12" t="n">
-        <v>0.0782</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>0.0774</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="D133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="E133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="F133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="G133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="H133" s="57" t="n">
-        <v>25.1348</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="D134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="E134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="F134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="G134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="H134" s="57" t="n">
-        <v>92.3738</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="D135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="E135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="F135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="G135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="H135" s="57" t="n">
-        <v>31.414</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="D139" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D140" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="D141" s="12" t="n">
-        <v>0.1235</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="D142" s="12" t="n">
-        <v>0.3602</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D143" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D144" s="58" t="n">
-        <v>0.7812</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D145" s="12" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D146" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="D147" s="12" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="D148" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D149" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I149" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="D150" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D151" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="2" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
-      <c r="I153" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D154" s="60" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="D155" s="61" t="n">
-        <v>1963.1806</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="D156" s="62" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="D157" s="56" t="n">
-        <v>46089.0479</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D158" s="63" t="s">
-        <v>770</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="C162" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="D162" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
-      <c r="I162" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="0" t="s">
-        <v>725</v>
-      </c>
-      <c r="C163" s="12" t="n">
-        <v>-0.0564</v>
-      </c>
-      <c r="D163" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="12" t="n">
-        <v>0.0378</v>
-      </c>
-      <c r="F163" s="12" t="n">
-        <v>0.0778</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C164" s="12" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="D164" s="12" t="n">
-        <v>0.0672</v>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>0.0809</v>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v>0.1529</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="D165" s="55" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="E165" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="55" t="n">
-        <v>-0.0156</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="C167" s="9"/>
-      <c r="D167" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E167" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="H167" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="I167" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="D168" s="12" t="n">
-        <v>0.0598</v>
-      </c>
-      <c r="E168" s="12" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="F168" s="12" t="n">
-        <v>0.0581</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>0.0573</v>
-      </c>
-      <c r="H168" s="12" t="n">
-        <v>0.0564</v>
-      </c>
-      <c r="I168" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="D169" s="56" t="n">
-        <v>268.999</v>
-      </c>
-      <c r="E169" s="56" t="n">
-        <v>268.999</v>
-      </c>
-      <c r="F169" s="56" t="n">
-        <v>268.999</v>
-      </c>
-      <c r="G169" s="56" t="n">
-        <v>268.999</v>
-      </c>
-      <c r="H169" s="56" t="n">
-        <v>268.999</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="0" t="s">
-        <v>730</v>
-      </c>
-      <c r="D170" s="12" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="E170" s="12" t="n">
-        <v>0.0483</v>
-      </c>
-      <c r="F170" s="12" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>0.0458</v>
-      </c>
-      <c r="H170" s="12" t="n">
-        <v>0.0446</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="D171" s="12" t="n">
-        <v>0.0826</v>
-      </c>
-      <c r="E171" s="12" t="n">
-        <v>0.0826</v>
-      </c>
-      <c r="F171" s="12" t="n">
-        <v>0.0826</v>
-      </c>
-      <c r="G171" s="12" t="n">
-        <v>0.0826</v>
-      </c>
-      <c r="H171" s="12" t="n">
-        <v>0.0826</v>
-      </c>
-      <c r="I171" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="D172" s="57" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="E172" s="57" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="F172" s="57" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="G172" s="57" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="H172" s="57" t="n">
-        <v>41.73</v>
-      </c>
-      <c r="I172" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="D173" s="57" t="n">
-        <v>94.8936</v>
-      </c>
-      <c r="E173" s="57" t="n">
-        <v>94.8936</v>
-      </c>
-      <c r="F173" s="57" t="n">
-        <v>94.8936</v>
-      </c>
-      <c r="G173" s="57" t="n">
-        <v>94.8936</v>
-      </c>
-      <c r="H173" s="57" t="n">
-        <v>94.8936</v>
-      </c>
-      <c r="I173" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="D174" s="57" t="n">
-        <v>40.711</v>
-      </c>
-      <c r="E174" s="57" t="n">
-        <v>40.711</v>
-      </c>
-      <c r="F174" s="57" t="n">
-        <v>40.711</v>
-      </c>
-      <c r="G174" s="57" t="n">
-        <v>40.711</v>
-      </c>
-      <c r="H174" s="57" t="n">
-        <v>40.711</v>
-      </c>
-      <c r="I174" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D175" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="C177" s="9"/>
-      <c r="D177" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E177" s="9"/>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
-      <c r="I177" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="D178" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D179" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I179" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="D180" s="12" t="n">
-        <v>0.1455</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="D181" s="12" t="n">
-        <v>0.4429</v>
-      </c>
-      <c r="I181" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="D182" s="12" t="n">
-        <v>0.1291</v>
-      </c>
-      <c r="I182" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="D183" s="58" t="n">
-        <v>1.0166</v>
-      </c>
-      <c r="I183" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="D184" s="12" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="I184" s="2" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="D185" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="0" t="s">
-        <v>736</v>
-      </c>
-      <c r="D186" s="12" t="n">
-        <v>0.4191</v>
-      </c>
-      <c r="I186" s="2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="D187" s="12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I187" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="D188" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I188" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="0" t="s">
-        <v>738</v>
-      </c>
-      <c r="D189" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="D190" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="9"/>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
-      <c r="I192" s="8" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="0" t="s">
-        <v>741</v>
-      </c>
-      <c r="D193" s="60" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I193" s="2" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B194" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="D194" s="61" t="n">
-        <v>1230.9427</v>
-      </c>
-      <c r="I194" s="2" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="D195" s="62" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="I195" s="2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="D196" s="56" t="n">
-        <v>8625.6879</v>
-      </c>
-      <c r="I196" s="2" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="D197" s="63" t="s">
-        <v>770</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>771</v>
+      <c r="B55" s="2" t="s">
+        <v>825</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=159978&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D6" r:id="rId2" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155313&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D7" r:id="rId3" display="https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=4170"/>
+    <hyperlink ref="D8" r:id="rId4" display="https://www.vale.com/pt/investidores"/>
+    <hyperlink ref="D9" r:id="rId5" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160568&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D10" r:id="rId6" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155288&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D11" r:id="rId7" display="https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=4030"/>
+    <hyperlink ref="D12" r:id="rId8" display="https://ri.csn.com.br"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160130&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D14" r:id="rId10" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=154830&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D15" r:id="rId11" display="https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=3980"/>
+    <hyperlink ref="D16" r:id="rId12" display="https://ri.gerdau.com"/>
+    <hyperlink ref="D17" r:id="rId13" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=159792&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D18" r:id="rId14" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=154757&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D19" r:id="rId15" display="https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=14320"/>
+    <hyperlink ref="D20" r:id="rId16" display="https://ri.usiminas.com"/>
+    <hyperlink ref="D21" r:id="rId17" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=160566&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D22" r:id="rId18" display="https://www.rad.cvm.gov.br/ENET/frmGerenciaPaginaFRE.aspx?NumeroSequencialDocumento=155318&amp;CodigoTipoInstituicao=1"/>
+    <hyperlink ref="D23" r:id="rId19" display="https://www.rad.cvm.gov.br/ENET/frmConsultaExternaCVM.aspx?codigoCVM=25585"/>
+    <hyperlink ref="D24" r:id="rId20" display="https://ri.csnmineracao.com.br"/>
+    <hyperlink ref="D27" r:id="rId21" display="https://dados.cvm.gov.br/dataset/cia_aberta-doc-dfp"/>
+    <hyperlink ref="D28" r:id="rId22" display="https://dados.cvm.gov.br/dataset/cia_aberta-doc-itr"/>
+    <hyperlink ref="D29" r:id="rId23" display="https://www.b3.com.br/pt_br/market-data-e-indices/servicos-de-dados/market-data/historico/mercado-a-vista/series-historicas/"/>
+    <hyperlink ref="D30" r:id="rId24" display="https://www.tesourotransparente.gov.br/ckan/dataset/taxas-dos-titulos-ofertados-pelo-tesouro-direto"/>
+    <hyperlink ref="D31" r:id="rId25" display="https://www.bcb.gov.br/publicacoes/focus"/>
+    <hyperlink ref="D32" r:id="rId26" display="https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/ctryprem.html"/>
+    <hyperlink ref="D33" r:id="rId27" display="https://www.worldbank.org/en/research/commodity-markets"/>
+    <hyperlink ref="D34" r:id="rId28" display="https://www3.bcb.gov.br/sgspub/"/>
+    <hyperlink ref="D35" r:id="rId29" display="https://www.latibex.com/docs/Documentos/LED/2023/03/02/BRACN_20230301_125502_B01_GGBR3_001_20230322_001_DOC001.pdf"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13744,6 +12027,2644 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B1:L197"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L4" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="48" t="str">
+        <f aca="false">"EM USO: "&amp;INDEX($L$5:$L$8,Painel!$Y$5)</f>
+        <v>EM USO: Vale (VALE3)</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="8"/>
+      <c r="L6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="C7" s="49" t="n">
+        <f aca="false">INDEX(C$1:C$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0209</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="49" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0378</v>
+      </c>
+      <c r="F7" s="49" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0683</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="49" t="n">
+        <f aca="false">INDEX(C$1:C$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.3459</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.3484</v>
+      </c>
+      <c r="E8" s="49" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.3936</v>
+      </c>
+      <c r="F8" s="49" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.4542</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0156</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-0.0156</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D12" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.083</v>
+      </c>
+      <c r="E12" s="49" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0815</v>
+      </c>
+      <c r="F12" s="49" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.08</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0785</v>
+      </c>
+      <c r="H12" s="49" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-1570</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-1570</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-1570</v>
+      </c>
+      <c r="G13" s="31" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-1570</v>
+      </c>
+      <c r="H13" s="31" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>-1570</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D14" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.146</v>
+      </c>
+      <c r="E14" s="49" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1449</v>
+      </c>
+      <c r="F14" s="49" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1438</v>
+      </c>
+      <c r="G14" s="49" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1427</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1415</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0569</v>
+      </c>
+      <c r="E15" s="49" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0569</v>
+      </c>
+      <c r="F15" s="49" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0569</v>
+      </c>
+      <c r="G15" s="49" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0569</v>
+      </c>
+      <c r="H15" s="49" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0569</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="50" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>21.598</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>21.598</v>
+      </c>
+      <c r="F16" s="50" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>21.598</v>
+      </c>
+      <c r="G16" s="50" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>21.598</v>
+      </c>
+      <c r="H16" s="50" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>21.598</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>98.067</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>98.067</v>
+      </c>
+      <c r="F17" s="50" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>98.067</v>
+      </c>
+      <c r="G17" s="50" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>98.067</v>
+      </c>
+      <c r="H17" s="50" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>98.067</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>91.9277</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>91.9277</v>
+      </c>
+      <c r="F18" s="50" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>91.9277</v>
+      </c>
+      <c r="G18" s="50" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>91.9277</v>
+      </c>
+      <c r="H18" s="50" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>91.9277</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <f aca="false">INDEX(E$1:E$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <f aca="false">INDEX(F$1:F$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <f aca="false">INDEX(G$1:G$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <f aca="false">INDEX(H$1:H$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="D23" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1291</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0936</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="D25" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.679</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.1291</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="D27" s="51" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.7558</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D28" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.0423</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D29" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D30" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.2625</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D31" s="49" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="D32" s="52" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>20038</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="D37" s="53" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D38" s="54" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>4072.366</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D39" s="41" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>67.64</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D40" s="31" t="n">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>275454.8362</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="D41" s="55" t="str">
+        <f aca="false">INDEX(D$1:D$200,ROW()+39*Painel!$Y$5)</f>
+        <v>2026-10-08</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D48" s="56" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E48" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="56" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="D52" s="57" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="E52" s="57" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="F52" s="57" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="G52" s="57" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="H52" s="57" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D55" s="58" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="E55" s="58" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="F55" s="58" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="G55" s="58" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="H55" s="58" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D56" s="58" t="n">
+        <v>98.067</v>
+      </c>
+      <c r="E56" s="58" t="n">
+        <v>98.067</v>
+      </c>
+      <c r="F56" s="58" t="n">
+        <v>98.067</v>
+      </c>
+      <c r="G56" s="58" t="n">
+        <v>98.067</v>
+      </c>
+      <c r="H56" s="58" t="n">
+        <v>98.067</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D57" s="58" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="E57" s="58" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="F57" s="58" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="G57" s="58" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="H57" s="58" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D58" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="D66" s="59" t="n">
+        <v>0.7558</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="D71" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D72" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="D73" s="57" t="n">
+        <v>20038</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="D76" s="61" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D77" s="62" t="n">
+        <v>4072.366</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D78" s="63" t="n">
+        <v>67.64</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D79" s="57" t="n">
+        <v>275454.8362</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="D80" s="64" t="s">
+        <v>875</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0.0778</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D87" s="56" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E87" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="56" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D90" s="12" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="D91" s="57" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="E91" s="57" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="F91" s="57" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="G91" s="57" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="H91" s="57" t="n">
+        <v>351.131</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D92" s="12" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" s="58" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="E94" s="58" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="F94" s="58" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="G94" s="58" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="H94" s="58" t="n">
+        <v>19.5303</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D95" s="58" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="E95" s="58" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="F95" s="58" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="G95" s="58" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="H95" s="58" t="n">
+        <v>135.0709</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" s="58" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="E96" s="58" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="F96" s="58" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="G96" s="58" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="H96" s="58" t="n">
+        <v>92.5353</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D97" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="D105" s="59" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="D110" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="D112" s="57" t="n">
+        <v>13101.338</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="D115" s="61" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D116" s="62" t="n">
+        <v>1326.0939</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D117" s="63" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D118" s="57" t="n">
+        <v>8433.9575</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="D119" s="64" t="s">
+        <v>875</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D126" s="56" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E126" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="56" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="D130" s="57" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="E130" s="57" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="F130" s="57" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="G130" s="57" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="H130" s="57" t="n">
+        <v>563.158</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.0782</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D133" s="58" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="E133" s="58" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="F133" s="58" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="G133" s="58" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="H133" s="58" t="n">
+        <v>25.1348</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D134" s="58" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="E134" s="58" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="F134" s="58" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="G134" s="58" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="H134" s="58" t="n">
+        <v>92.3738</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D135" s="58" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="E135" s="58" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="F135" s="58" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="G135" s="58" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="H135" s="58" t="n">
+        <v>31.414</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="9"/>
+      <c r="I138" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="D140" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D141" s="12" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="D142" s="12" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="D143" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="D144" s="59" t="n">
+        <v>0.7812</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D146" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D148" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="D149" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D150" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="D151" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
+      <c r="I153" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="D154" s="61" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D155" s="62" t="n">
+        <v>1963.1806</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D156" s="63" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D157" s="57" t="n">
+        <v>46089.0479</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="D158" s="64" t="s">
+        <v>875</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="9"/>
+      <c r="H162" s="9"/>
+      <c r="I162" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="C163" s="12" t="n">
+        <v>-0.0564</v>
+      </c>
+      <c r="D163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>0.0778</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" s="12" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="D164" s="12" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="E164" s="12" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D165" s="56" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E165" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="56" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C167" s="9"/>
+      <c r="D167" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D168" s="12" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="H168" s="12" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="D169" s="57" t="n">
+        <v>268.999</v>
+      </c>
+      <c r="E169" s="57" t="n">
+        <v>268.999</v>
+      </c>
+      <c r="F169" s="57" t="n">
+        <v>268.999</v>
+      </c>
+      <c r="G169" s="57" t="n">
+        <v>268.999</v>
+      </c>
+      <c r="H169" s="57" t="n">
+        <v>268.999</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D170" s="12" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="E170" s="12" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="H170" s="12" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="D171" s="12" t="n">
+        <v>0.0826</v>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>0.0826</v>
+      </c>
+      <c r="F171" s="12" t="n">
+        <v>0.0826</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.0826</v>
+      </c>
+      <c r="H171" s="12" t="n">
+        <v>0.0826</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D172" s="58" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="E172" s="58" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="F172" s="58" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="G172" s="58" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="H172" s="58" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D173" s="58" t="n">
+        <v>94.8936</v>
+      </c>
+      <c r="E173" s="58" t="n">
+        <v>94.8936</v>
+      </c>
+      <c r="F173" s="58" t="n">
+        <v>94.8936</v>
+      </c>
+      <c r="G173" s="58" t="n">
+        <v>94.8936</v>
+      </c>
+      <c r="H173" s="58" t="n">
+        <v>94.8936</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="D174" s="58" t="n">
+        <v>40.711</v>
+      </c>
+      <c r="E174" s="58" t="n">
+        <v>40.711</v>
+      </c>
+      <c r="F174" s="58" t="n">
+        <v>40.711</v>
+      </c>
+      <c r="G174" s="58" t="n">
+        <v>40.711</v>
+      </c>
+      <c r="H174" s="58" t="n">
+        <v>40.711</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D175" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E177" s="9"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="9"/>
+      <c r="I177" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="0" t="s">
+        <v>365</v>
+      </c>
+      <c r="D178" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="D179" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D180" s="12" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="D181" s="12" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="D182" s="12" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B183" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="D183" s="59" t="n">
+        <v>1.0166</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B184" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D184" s="12" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B185" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D185" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B186" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D186" s="12" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D187" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B188" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="D188" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B189" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="D189" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="D190" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
+      <c r="I192" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B193" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="D193" s="61" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B194" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D194" s="62" t="n">
+        <v>1230.9427</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D195" s="63" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D196" s="57" t="n">
+        <v>8625.6879</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="D197" s="64" t="s">
+        <v>875</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B1:K146"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -13754,16 +14675,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>783</v>
+        <v>888</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>784</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="48" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14856,7 +15777,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="47" t="s">
+      <c r="B40" s="48" t="s">
         <v>9</v>
       </c>
     </row>
@@ -15949,7 +16870,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="48" t="s">
         <v>10</v>
       </c>
     </row>
@@ -17042,7 +17963,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="47" t="s">
+      <c r="B112" s="48" t="s">
         <v>11</v>
       </c>
     </row>
